--- a/examples/Agilent/ใบสั่งงาน JOB 7.xlsx
+++ b/examples/Agilent/ใบสั่งงาน JOB 7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ffa44234d445c58/Contract mfg/Agilent/A1 ใบสั่งงาน/ใบสั่งงานฉบับแก้ไข/ฟอร์มใบสั่งงาน/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\Agilent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{FF2FDDB1-DE1B-4A4D-9D7A-B89D81192A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6827091C-52B5-4E7C-83F0-5D3D65FE8DEC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DA1D8-D1D8-45A9-8083-E20355BFA7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="958" activeTab="1" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
+    <workbookView xWindow="-28800" yWindow="480" windowWidth="28800" windowHeight="15150" tabRatio="958" activeTab="1" xr2:uid="{4F180DBB-2D27-44A5-BB20-72766F3B0AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="ใบงาน Agilent_JOB 7.1" sheetId="34" r:id="rId1"/>
@@ -35,7 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1197,7 +1196,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1448,15 +1447,310 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1478,338 +1772,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1915,9 +1915,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1289050</xdr:colOff>
+      <xdr:colOff>1287145</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>26669</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2043,9 +2043,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1289050</xdr:colOff>
+      <xdr:colOff>1287145</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:rowOff>26669</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2362,9 +2362,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2402,7 +2402,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2508,7 +2508,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2650,7 +2650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2659,108 +2659,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF1C0A7-AD3A-4D03-BC3A-AC8B2D9466E4}">
   <dimension ref="A1:O69"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="2"/>
-    <col min="2" max="2" width="21.265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.73046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.265625" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.73046875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.73046875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.73046875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.73046875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.73046875" style="2" customWidth="1"/>
-    <col min="12" max="13" width="8.73046875" style="1" customWidth="1"/>
-    <col min="14" max="15" width="13.73046875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.3984375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="2"/>
+    <col min="2" max="2" width="21.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" style="2" customWidth="1"/>
+    <col min="12" max="13" width="8.77734375" style="1" customWidth="1"/>
+    <col min="14" max="15" width="13.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-    </row>
-    <row r="2" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-    </row>
-    <row r="3" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A3" s="125"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="125"/>
-    </row>
-    <row r="4" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
-      <c r="N4" s="125"/>
-    </row>
-    <row r="5" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A5" s="125"/>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="125"/>
-      <c r="N5" s="125"/>
-    </row>
-    <row r="6" spans="1:15" ht="22.5">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+    </row>
+    <row r="2" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+    </row>
+    <row r="3" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A3" s="98"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+    </row>
+    <row r="4" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+    </row>
+    <row r="5" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -2773,7 +2773,9 @@
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="76"/>
+      <c r="B7" s="97">
+        <v>46242</v>
+      </c>
       <c r="C7" s="49"/>
       <c r="D7" s="8" t="s">
         <v>66</v>
@@ -2867,10 +2869,10 @@
       <c r="F11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="109"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
     </row>
     <row r="12" spans="1:15" s="7" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="8"/>
@@ -2915,44 +2917,44 @@
       <c r="O14" s="14"/>
     </row>
     <row r="15" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="134" t="s">
+      <c r="D15" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="138" t="s">
+      <c r="E15" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="140" t="s">
+      <c r="F15" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="G15" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="131" t="s">
+      <c r="H15" s="106" t="s">
         <v>32</v>
       </c>
       <c r="J15" s="92"/>
-      <c r="K15" s="133"/>
+      <c r="K15" s="108"/>
     </row>
     <row r="16" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="134"/>
-      <c r="B16" s="137"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="132"/>
+      <c r="A16" s="109"/>
+      <c r="B16" s="112"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="107"/>
       <c r="J16" s="92"/>
-      <c r="K16" s="133"/>
+      <c r="K16" s="108"/>
     </row>
     <row r="17" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="19">
@@ -2982,7 +2984,7 @@
         <f>G17*0.00328/F17</f>
         <v>101.2864</v>
       </c>
-      <c r="K17" s="124" t="s">
+      <c r="K17" s="99" t="s">
         <v>83</v>
       </c>
       <c r="L17" s="7"/>
@@ -3001,7 +3003,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="124"/>
+      <c r="K18" s="99"/>
       <c r="L18" s="7"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
@@ -3172,45 +3174,45 @@
       <c r="O27" s="14"/>
     </row>
     <row r="28" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="134" t="s">
+      <c r="A28" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="134" t="s">
+      <c r="B28" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="134" t="s">
+      <c r="C28" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="134" t="s">
+      <c r="D28" s="109" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="89"/>
-      <c r="F28" s="135" t="s">
+      <c r="F28" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="129" t="s">
+      <c r="G28" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="129" t="s">
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="129" t="s">
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104" t="s">
         <v>68</v>
       </c>
       <c r="O28" s="94"/>
     </row>
     <row r="29" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
+      <c r="A29" s="109"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
       <c r="E29" s="89"/>
-      <c r="F29" s="135"/>
+      <c r="F29" s="110"/>
       <c r="G29" s="90" t="s">
         <v>71</v>
       </c>
@@ -3232,24 +3234,24 @@
       <c r="M29" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="129"/>
+      <c r="N29" s="104"/>
       <c r="O29" s="94"/>
     </row>
     <row r="30" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="126">
+      <c r="A30" s="101">
         <v>7.1</v>
       </c>
-      <c r="B30" s="157" t="s">
+      <c r="B30" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="160" t="s">
+      <c r="C30" s="136" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="163">
+      <c r="D30" s="139">
         <v>2</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="166">
+      <c r="F30" s="142">
         <f>N8*D30</f>
         <v>4000</v>
       </c>
@@ -3257,7 +3259,7 @@
       <c r="H30" s="58"/>
       <c r="I30" s="58"/>
       <c r="J30" s="59"/>
-      <c r="K30" s="156" t="s">
+      <c r="K30" s="132" t="s">
         <v>56</v>
       </c>
       <c r="L30" s="10"/>
@@ -3266,119 +3268,119 @@
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="127"/>
-      <c r="B31" s="158"/>
-      <c r="C31" s="161"/>
-      <c r="D31" s="164"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="140"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="167"/>
+      <c r="F31" s="143"/>
       <c r="G31" s="58"/>
       <c r="H31" s="58"/>
       <c r="I31" s="58"/>
       <c r="J31" s="59"/>
-      <c r="K31" s="156"/>
+      <c r="K31" s="132"/>
       <c r="L31" s="12"/>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="127"/>
-      <c r="B32" s="158"/>
-      <c r="C32" s="161"/>
-      <c r="D32" s="164"/>
+      <c r="A32" s="102"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="140"/>
       <c r="E32" s="21"/>
-      <c r="F32" s="167"/>
+      <c r="F32" s="143"/>
       <c r="G32" s="58"/>
       <c r="H32" s="58"/>
       <c r="I32" s="58"/>
       <c r="J32" s="59"/>
-      <c r="K32" s="156"/>
+      <c r="K32" s="132"/>
       <c r="L32" s="21"/>
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="127"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="164"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="140"/>
       <c r="E33" s="21"/>
-      <c r="F33" s="167"/>
+      <c r="F33" s="143"/>
       <c r="G33" s="58"/>
       <c r="H33" s="58"/>
       <c r="I33" s="58"/>
       <c r="J33" s="59"/>
-      <c r="K33" s="156"/>
+      <c r="K33" s="132"/>
       <c r="L33" s="21"/>
       <c r="M33" s="21"/>
       <c r="N33" s="21"/>
       <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="127"/>
-      <c r="B34" s="158"/>
-      <c r="C34" s="161"/>
-      <c r="D34" s="164"/>
+      <c r="A34" s="102"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="140"/>
       <c r="E34" s="21"/>
-      <c r="F34" s="167"/>
+      <c r="F34" s="143"/>
       <c r="G34" s="58"/>
       <c r="H34" s="58"/>
       <c r="I34" s="58"/>
       <c r="J34" s="59"/>
-      <c r="K34" s="156"/>
+      <c r="K34" s="132"/>
       <c r="L34" s="21"/>
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="127"/>
-      <c r="B35" s="158"/>
-      <c r="C35" s="161"/>
-      <c r="D35" s="164"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="134"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="140"/>
       <c r="E35" s="21"/>
-      <c r="F35" s="167"/>
+      <c r="F35" s="143"/>
       <c r="G35" s="58"/>
       <c r="H35" s="58"/>
       <c r="I35" s="58"/>
       <c r="J35" s="59"/>
-      <c r="K35" s="156"/>
+      <c r="K35" s="132"/>
       <c r="L35" s="21"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="127"/>
-      <c r="B36" s="158"/>
-      <c r="C36" s="161"/>
-      <c r="D36" s="164"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="134"/>
+      <c r="C36" s="137"/>
+      <c r="D36" s="140"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="167"/>
+      <c r="F36" s="143"/>
       <c r="G36" s="58"/>
       <c r="H36" s="58"/>
       <c r="I36" s="58"/>
       <c r="J36" s="59"/>
-      <c r="K36" s="156"/>
+      <c r="K36" s="132"/>
       <c r="L36" s="21"/>
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="128"/>
-      <c r="B37" s="159"/>
-      <c r="C37" s="162"/>
-      <c r="D37" s="165"/>
+      <c r="A37" s="103"/>
+      <c r="B37" s="135"/>
+      <c r="C37" s="138"/>
+      <c r="D37" s="141"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="168"/>
+      <c r="F37" s="144"/>
       <c r="G37" s="58"/>
       <c r="H37" s="58"/>
       <c r="I37" s="58"/>
       <c r="J37" s="59"/>
-      <c r="K37" s="156"/>
+      <c r="K37" s="132"/>
       <c r="L37" s="21"/>
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
@@ -3418,74 +3420,74 @@
       <c r="O40" s="14"/>
     </row>
     <row r="41" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="C41" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="145" t="s">
+      <c r="D41" s="121" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="27"/>
-      <c r="F41" s="113" t="s">
+      <c r="F41" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="113" t="s">
+      <c r="G41" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="148" t="s">
+      <c r="H41" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="148" t="s">
+      <c r="I41" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="148" t="s">
+      <c r="J41" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="148" t="s">
+      <c r="K41" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="L41" s="151" t="s">
+      <c r="L41" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="152"/>
-      <c r="N41" s="142" t="s">
+      <c r="M41" s="128"/>
+      <c r="N41" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="142"/>
+      <c r="O41" s="117"/>
     </row>
     <row r="42" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="146"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
-      <c r="K42" s="149"/>
-      <c r="L42" s="153"/>
-      <c r="M42" s="154"/>
-      <c r="N42" s="142"/>
-      <c r="O42" s="142"/>
+      <c r="A42" s="119"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="119"/>
+      <c r="D42" s="122"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="119"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="129"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="117"/>
     </row>
     <row r="43" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="144"/>
-      <c r="B43" s="144"/>
-      <c r="C43" s="144"/>
-      <c r="D43" s="147"/>
+      <c r="A43" s="120"/>
+      <c r="B43" s="120"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="123"/>
       <c r="E43" s="29"/>
-      <c r="F43" s="144"/>
-      <c r="G43" s="144"/>
-      <c r="H43" s="150"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="150"/>
-      <c r="K43" s="150"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="126"/>
       <c r="L43" s="28" t="s">
         <v>23</v>
       </c>
@@ -3854,108 +3856,108 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5CCEBF-EE4D-40EB-93FC-3C9B4F6B4647}">
   <dimension ref="A1:O67"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="2"/>
-    <col min="2" max="2" width="21.265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.73046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.265625" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.73046875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.73046875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.73046875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.73046875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.73046875" style="2" customWidth="1"/>
-    <col min="12" max="13" width="8.73046875" style="1" customWidth="1"/>
-    <col min="14" max="15" width="13.73046875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.3984375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.73046875" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="2"/>
+    <col min="2" max="2" width="21.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" style="2" customWidth="1"/>
+    <col min="12" max="13" width="8.77734375" style="1" customWidth="1"/>
+    <col min="14" max="15" width="13.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-    </row>
-    <row r="2" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-    </row>
-    <row r="3" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A3" s="125"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="125"/>
-    </row>
-    <row r="4" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
-      <c r="N4" s="125"/>
-    </row>
-    <row r="5" spans="1:15" ht="11.65" customHeight="1">
-      <c r="A5" s="125"/>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="125"/>
-      <c r="M5" s="125"/>
-      <c r="N5" s="125"/>
-    </row>
-    <row r="6" spans="1:15" ht="22.5">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+    </row>
+    <row r="2" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+    </row>
+    <row r="3" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A3" s="98"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+    </row>
+    <row r="4" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+    </row>
+    <row r="5" spans="1:15" ht="11.7" customHeight="1">
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.8">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -3968,7 +3970,9 @@
       <c r="A7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="85"/>
+      <c r="B7" s="97">
+        <v>46242</v>
+      </c>
       <c r="C7" s="86"/>
       <c r="D7" s="61" t="s">
         <v>66</v>
@@ -4109,44 +4113,44 @@
       <c r="O14" s="14"/>
     </row>
     <row r="15" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="134" t="s">
+      <c r="D15" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="138" t="s">
+      <c r="E15" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="140" t="s">
+      <c r="F15" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="G15" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="131" t="s">
+      <c r="H15" s="106" t="s">
         <v>32</v>
       </c>
       <c r="J15" s="92"/>
-      <c r="K15" s="133"/>
+      <c r="K15" s="108"/>
     </row>
     <row r="16" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="134"/>
-      <c r="B16" s="137"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="132"/>
+      <c r="A16" s="109"/>
+      <c r="B16" s="112"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="107"/>
       <c r="J16" s="92"/>
-      <c r="K16" s="133"/>
+      <c r="K16" s="108"/>
     </row>
     <row r="17" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
       <c r="A17" s="39">
@@ -4176,7 +4180,7 @@
         <f>G17*0.00328/F17</f>
         <v>43.97824</v>
       </c>
-      <c r="K17" s="124" t="s">
+      <c r="K17" s="99" t="s">
         <v>83</v>
       </c>
       <c r="L17" s="7"/>
@@ -4195,7 +4199,7 @@
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
       <c r="J18" s="14"/>
-      <c r="K18" s="124"/>
+      <c r="K18" s="99"/>
       <c r="L18" s="7"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
@@ -4368,45 +4372,45 @@
       <c r="O27" s="14"/>
     </row>
     <row r="28" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="134" t="s">
+      <c r="A28" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="134" t="s">
+      <c r="B28" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="134" t="s">
+      <c r="C28" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="134" t="s">
+      <c r="D28" s="109" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="89"/>
-      <c r="F28" s="135" t="s">
+      <c r="F28" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="129" t="s">
+      <c r="G28" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="129"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="129" t="s">
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="129" t="s">
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104" t="s">
         <v>68</v>
       </c>
       <c r="O28" s="94"/>
     </row>
     <row r="29" spans="1:15" s="91" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
+      <c r="A29" s="109"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
       <c r="E29" s="89"/>
-      <c r="F29" s="135"/>
+      <c r="F29" s="110"/>
       <c r="G29" s="90" t="s">
         <v>71</v>
       </c>
@@ -4428,24 +4432,24 @@
       <c r="M29" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="129"/>
+      <c r="N29" s="104"/>
       <c r="O29" s="94"/>
     </row>
     <row r="30" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="126">
+      <c r="A30" s="101">
         <v>7.2</v>
       </c>
-      <c r="B30" s="157" t="s">
+      <c r="B30" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="169" t="s">
+      <c r="C30" s="145" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="163">
+      <c r="D30" s="139">
         <v>1</v>
       </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="166">
+      <c r="F30" s="142">
         <f>N8*D30</f>
         <v>2000</v>
       </c>
@@ -4453,7 +4457,7 @@
       <c r="H30" s="58"/>
       <c r="I30" s="58"/>
       <c r="J30" s="59"/>
-      <c r="K30" s="156" t="s">
+      <c r="K30" s="132" t="s">
         <v>58</v>
       </c>
       <c r="L30" s="10"/>
@@ -4462,119 +4466,119 @@
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="127"/>
-      <c r="B31" s="158"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="164"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="140"/>
       <c r="E31" s="21"/>
-      <c r="F31" s="167"/>
+      <c r="F31" s="143"/>
       <c r="G31" s="58"/>
       <c r="H31" s="58"/>
       <c r="I31" s="58"/>
       <c r="J31" s="59"/>
-      <c r="K31" s="156"/>
+      <c r="K31" s="132"/>
       <c r="L31" s="12"/>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="127"/>
-      <c r="B32" s="158"/>
-      <c r="C32" s="170"/>
-      <c r="D32" s="164"/>
+      <c r="A32" s="102"/>
+      <c r="B32" s="134"/>
+      <c r="C32" s="146"/>
+      <c r="D32" s="140"/>
       <c r="E32" s="12"/>
-      <c r="F32" s="167"/>
+      <c r="F32" s="143"/>
       <c r="G32" s="58"/>
       <c r="H32" s="58"/>
       <c r="I32" s="58"/>
       <c r="J32" s="59"/>
-      <c r="K32" s="156"/>
+      <c r="K32" s="132"/>
       <c r="L32" s="21"/>
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="127"/>
-      <c r="B33" s="158"/>
-      <c r="C33" s="170"/>
-      <c r="D33" s="164"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="134"/>
+      <c r="C33" s="146"/>
+      <c r="D33" s="140"/>
       <c r="E33" s="12"/>
-      <c r="F33" s="167"/>
+      <c r="F33" s="143"/>
       <c r="G33" s="58"/>
       <c r="H33" s="58"/>
       <c r="I33" s="58"/>
       <c r="J33" s="59"/>
-      <c r="K33" s="156"/>
+      <c r="K33" s="132"/>
       <c r="L33" s="21"/>
       <c r="M33" s="21"/>
       <c r="N33" s="21"/>
       <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="127"/>
-      <c r="B34" s="158"/>
-      <c r="C34" s="170"/>
-      <c r="D34" s="164"/>
+      <c r="A34" s="102"/>
+      <c r="B34" s="134"/>
+      <c r="C34" s="146"/>
+      <c r="D34" s="140"/>
       <c r="E34" s="12"/>
-      <c r="F34" s="167"/>
+      <c r="F34" s="143"/>
       <c r="G34" s="58"/>
       <c r="H34" s="58"/>
       <c r="I34" s="58"/>
       <c r="J34" s="59"/>
-      <c r="K34" s="156"/>
+      <c r="K34" s="132"/>
       <c r="L34" s="21"/>
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="127"/>
-      <c r="B35" s="158"/>
-      <c r="C35" s="170"/>
-      <c r="D35" s="164"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="134"/>
+      <c r="C35" s="146"/>
+      <c r="D35" s="140"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="167"/>
+      <c r="F35" s="143"/>
       <c r="G35" s="58"/>
       <c r="H35" s="58"/>
       <c r="I35" s="58"/>
       <c r="J35" s="59"/>
-      <c r="K35" s="156"/>
+      <c r="K35" s="132"/>
       <c r="L35" s="21"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="127"/>
-      <c r="B36" s="158"/>
-      <c r="C36" s="170"/>
-      <c r="D36" s="164"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="134"/>
+      <c r="C36" s="146"/>
+      <c r="D36" s="140"/>
       <c r="E36" s="12"/>
-      <c r="F36" s="167"/>
+      <c r="F36" s="143"/>
       <c r="G36" s="58"/>
       <c r="H36" s="58"/>
       <c r="I36" s="58"/>
       <c r="J36" s="59"/>
-      <c r="K36" s="156"/>
+      <c r="K36" s="132"/>
       <c r="L36" s="21"/>
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" s="15" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="128"/>
-      <c r="B37" s="159"/>
-      <c r="C37" s="171"/>
-      <c r="D37" s="165"/>
+      <c r="A37" s="103"/>
+      <c r="B37" s="135"/>
+      <c r="C37" s="147"/>
+      <c r="D37" s="141"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="168"/>
+      <c r="F37" s="144"/>
       <c r="G37" s="58"/>
       <c r="H37" s="58"/>
       <c r="I37" s="58"/>
       <c r="J37" s="59"/>
-      <c r="K37" s="156"/>
+      <c r="K37" s="132"/>
       <c r="L37" s="21"/>
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
@@ -4614,74 +4618,74 @@
       <c r="O40" s="14"/>
     </row>
     <row r="41" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="C41" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="145" t="s">
+      <c r="D41" s="121" t="s">
         <v>19</v>
       </c>
       <c r="E41" s="27"/>
-      <c r="F41" s="113" t="s">
+      <c r="F41" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="113" t="s">
+      <c r="G41" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="148" t="s">
+      <c r="H41" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="148" t="s">
+      <c r="I41" s="124" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="148" t="s">
+      <c r="J41" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="148" t="s">
+      <c r="K41" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="L41" s="151" t="s">
+      <c r="L41" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="M41" s="152"/>
-      <c r="N41" s="142" t="s">
+      <c r="M41" s="128"/>
+      <c r="N41" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="O41" s="142"/>
+      <c r="O41" s="117"/>
     </row>
     <row r="42" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A42" s="143"/>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="146"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
-      <c r="K42" s="149"/>
-      <c r="L42" s="153"/>
-      <c r="M42" s="154"/>
-      <c r="N42" s="142"/>
-      <c r="O42" s="142"/>
+      <c r="A42" s="119"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="119"/>
+      <c r="D42" s="122"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="119"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="129"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="117"/>
     </row>
     <row r="43" spans="1:15" s="17" customFormat="1" ht="21" hidden="1" customHeight="1">
-      <c r="A43" s="144"/>
-      <c r="B43" s="144"/>
-      <c r="C43" s="144"/>
-      <c r="D43" s="147"/>
+      <c r="A43" s="120"/>
+      <c r="B43" s="120"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="123"/>
       <c r="E43" s="29"/>
-      <c r="F43" s="144"/>
-      <c r="G43" s="144"/>
-      <c r="H43" s="150"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="150"/>
-      <c r="K43" s="150"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="126"/>
       <c r="L43" s="28" t="s">
         <v>23</v>
       </c>
@@ -5032,205 +5036,205 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49C6252-8E67-46A6-BD75-369D1A7276BB}">
   <dimension ref="A1:Z83"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="75" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="20" width="3.19921875" customWidth="1"/>
-    <col min="21" max="26" width="5.46484375" customWidth="1"/>
-    <col min="28" max="28" width="15.3984375" customWidth="1"/>
+    <col min="3" max="20" width="3.21875" customWidth="1"/>
+    <col min="21" max="26" width="5.44140625" customWidth="1"/>
+    <col min="28" max="28" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
       <c r="W1" s="60"/>
       <c r="X1" s="60"/>
       <c r="Y1" s="60"/>
       <c r="Z1" s="60"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="119"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
+      <c r="A2" s="212"/>
+      <c r="B2" s="212"/>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="212"/>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
       <c r="W2" s="60"/>
       <c r="X2" s="60"/>
       <c r="Y2" s="60"/>
       <c r="Z2" s="60"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="119"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="212"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
       <c r="W3" s="60"/>
       <c r="X3" s="60"/>
       <c r="Y3" s="60"/>
       <c r="Z3" s="60"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119"/>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
+      <c r="A4" s="212"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="212"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
       <c r="Y4" s="60"/>
       <c r="Z4" s="60"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1">
-      <c r="A5" s="119"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
-      <c r="N5" s="119"/>
-      <c r="O5" s="119"/>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="119"/>
+      <c r="A5" s="212"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="M5" s="212"/>
+      <c r="N5" s="212"/>
+      <c r="O5" s="212"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="212"/>
+      <c r="S5" s="212"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="212"/>
       <c r="W5" s="60"/>
       <c r="X5" s="60"/>
       <c r="Y5" s="60"/>
       <c r="Z5" s="60"/>
     </row>
-    <row r="6" spans="1:26" ht="29.65">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="213" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="120"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="120"/>
-      <c r="P6" s="120"/>
-      <c r="Q6" s="120"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="120"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
+      <c r="H6" s="213"/>
+      <c r="I6" s="213"/>
+      <c r="J6" s="213"/>
+      <c r="K6" s="213"/>
+      <c r="L6" s="213"/>
+      <c r="M6" s="213"/>
+      <c r="N6" s="213"/>
+      <c r="O6" s="213"/>
+      <c r="P6" s="213"/>
+      <c r="Q6" s="213"/>
+      <c r="R6" s="213"/>
+      <c r="S6" s="213"/>
+      <c r="T6" s="213"/>
+      <c r="U6" s="213"/>
+      <c r="V6" s="213"/>
+      <c r="W6" s="213"/>
+      <c r="X6" s="213"/>
+      <c r="Y6" s="213"/>
+      <c r="Z6" s="213"/>
     </row>
     <row r="7" spans="1:26" s="63" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="214" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="123"/>
+      <c r="B7" s="214"/>
       <c r="C7" s="82" t="s">
         <v>80</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="111" t="str">
+      <c r="G7" s="205" t="str">
         <f>'ใบงาน Agilent_JOB 7.1'!F7</f>
         <v>xxx</v>
       </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -5238,7 +5242,7 @@
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
-      <c r="S7" s="216" t="s">
+      <c r="S7" s="96" t="s">
         <v>67</v>
       </c>
       <c r="W7" s="86" t="str">
@@ -5263,13 +5267,13 @@
       <c r="D8" s="56"/>
       <c r="E8" s="56"/>
       <c r="F8" s="56"/>
-      <c r="G8" s="122" t="str">
+      <c r="G8" s="215" t="str">
         <f>'ใบงาน Agilent_JOB 7.1'!F9</f>
         <v>K9801-60087</v>
       </c>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
+      <c r="H8" s="215"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="215"/>
       <c r="K8" s="56"/>
       <c r="L8" s="56"/>
       <c r="M8" s="56"/>
@@ -5282,17 +5286,17 @@
       <c r="T8" s="56"/>
     </row>
     <row r="9" spans="1:26" s="7" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="121" t="s">
+      <c r="A9" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="121"/>
-      <c r="G9" s="122" t="str">
+      <c r="B9" s="216"/>
+      <c r="G9" s="215" t="str">
         <f>'ใบงาน Agilent_JOB 7.2'!F9</f>
         <v>K9801-60116</v>
       </c>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="215"/>
+      <c r="J9" s="215"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
       <c r="N9" s="14"/>
@@ -5300,12 +5304,12 @@
       <c r="P9" s="14"/>
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
-      <c r="S9" s="124" t="s">
+      <c r="S9" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="T9" s="124"/>
-      <c r="U9" s="124"/>
-      <c r="V9" s="124"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
     </row>
     <row r="10" spans="1:26" s="7" customFormat="1" ht="21" customHeight="1">
       <c r="A10" s="8" t="s">
@@ -5316,17 +5320,17 @@
         <v>2000</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="111" t="s">
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="205"/>
+      <c r="J10" s="205"/>
       <c r="K10" s="57"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
@@ -5335,24 +5339,24 @@
       <c r="P10" s="14"/>
       <c r="Q10" s="14"/>
       <c r="R10" s="14"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-    </row>
-    <row r="11" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="S10" s="99"/>
+      <c r="T10" s="99"/>
+      <c r="U10" s="99"/>
+      <c r="V10" s="99"/>
+    </row>
+    <row r="11" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A11" s="14"/>
       <c r="B11" s="15"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="111" t="s">
+      <c r="G11" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
@@ -5364,7 +5368,7 @@
       <c r="S11" s="14"/>
       <c r="T11" s="14"/>
     </row>
-    <row r="12" spans="1:26" s="7" customFormat="1" ht="13.5">
+    <row r="12" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A12" s="14" t="s">
         <v>99</v>
       </c>
@@ -5373,12 +5377,12 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="111" t="s">
+      <c r="G12" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="205"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
@@ -5390,7 +5394,7 @@
       <c r="S12" s="14"/>
       <c r="T12" s="14"/>
     </row>
-    <row r="13" spans="1:26" s="7" customFormat="1" ht="13.5">
+    <row r="13" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="14"/>
@@ -5412,259 +5416,259 @@
       <c r="S13" s="14"/>
       <c r="T13" s="14"/>
     </row>
-    <row r="14" spans="1:26" s="7" customFormat="1" ht="13.5">
-      <c r="A14" s="112" t="s">
+    <row r="14" spans="1:26" s="7" customFormat="1" ht="13.8">
+      <c r="A14" s="206" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="99" t="s">
+      <c r="C14" s="198" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="99" t="s">
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="207"/>
+      <c r="G14" s="207"/>
+      <c r="H14" s="208"/>
+      <c r="I14" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="99" t="s">
+      <c r="J14" s="207"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="208"/>
+      <c r="O14" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="100"/>
-      <c r="T14" s="101"/>
-      <c r="U14" s="105" t="s">
+      <c r="P14" s="199"/>
+      <c r="Q14" s="199"/>
+      <c r="R14" s="199"/>
+      <c r="S14" s="199"/>
+      <c r="T14" s="200"/>
+      <c r="U14" s="204" t="s">
         <v>88</v>
       </c>
-      <c r="V14" s="105"/>
-      <c r="W14" s="105"/>
-      <c r="X14" s="105"/>
-      <c r="Y14" s="105"/>
-      <c r="Z14" s="105"/>
-    </row>
-    <row r="15" spans="1:26" s="7" customFormat="1" ht="13.5">
-      <c r="A15" s="113"/>
-      <c r="B15" s="112"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="104"/>
-      <c r="U15" s="105"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="105"/>
-      <c r="X15" s="105"/>
-      <c r="Y15" s="105"/>
-      <c r="Z15" s="105"/>
-    </row>
-    <row r="16" spans="1:26" s="65" customFormat="1" ht="35.65" customHeight="1">
+      <c r="V14" s="204"/>
+      <c r="W14" s="204"/>
+      <c r="X14" s="204"/>
+      <c r="Y14" s="204"/>
+      <c r="Z14" s="204"/>
+    </row>
+    <row r="15" spans="1:26" s="7" customFormat="1" ht="13.8">
+      <c r="A15" s="118"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
+      <c r="F15" s="210"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="209"/>
+      <c r="J15" s="210"/>
+      <c r="K15" s="210"/>
+      <c r="L15" s="210"/>
+      <c r="M15" s="210"/>
+      <c r="N15" s="211"/>
+      <c r="O15" s="201"/>
+      <c r="P15" s="202"/>
+      <c r="Q15" s="202"/>
+      <c r="R15" s="202"/>
+      <c r="S15" s="202"/>
+      <c r="T15" s="203"/>
+      <c r="U15" s="204"/>
+      <c r="V15" s="204"/>
+      <c r="W15" s="204"/>
+      <c r="X15" s="204"/>
+      <c r="Y15" s="204"/>
+      <c r="Z15" s="204"/>
+    </row>
+    <row r="16" spans="1:26" s="65" customFormat="1" ht="35.700000000000003" customHeight="1">
       <c r="A16" s="66">
         <v>1</v>
       </c>
       <c r="B16" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98" t="s">
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="193"/>
+      <c r="G16" s="193"/>
+      <c r="H16" s="193"/>
+      <c r="I16" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="193"/>
+      <c r="L16" s="193"/>
+      <c r="M16" s="193"/>
+      <c r="N16" s="193"/>
+      <c r="O16" s="193"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="193"/>
+      <c r="R16" s="193"/>
+      <c r="S16" s="193"/>
+      <c r="T16" s="193"/>
+      <c r="U16" s="193"/>
+      <c r="V16" s="193"/>
+      <c r="W16" s="193"/>
+      <c r="X16" s="193"/>
+      <c r="Y16" s="193"/>
+      <c r="Z16" s="193"/>
     </row>
     <row r="17" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="195">
         <v>2</v>
       </c>
       <c r="B17" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="193"/>
+      <c r="G17" s="193"/>
+      <c r="H17" s="193"/>
+      <c r="I17" s="193"/>
+      <c r="J17" s="193"/>
+      <c r="K17" s="193"/>
+      <c r="L17" s="193"/>
+      <c r="M17" s="193"/>
+      <c r="N17" s="193"/>
+      <c r="O17" s="193"/>
+      <c r="P17" s="193"/>
+      <c r="Q17" s="193"/>
+      <c r="R17" s="193"/>
+      <c r="S17" s="193"/>
+      <c r="T17" s="193"/>
+      <c r="U17" s="193"/>
+      <c r="V17" s="193"/>
+      <c r="W17" s="193"/>
+      <c r="X17" s="193"/>
+      <c r="Y17" s="193"/>
+      <c r="Z17" s="193"/>
     </row>
     <row r="18" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A18" s="107"/>
+      <c r="A18" s="196"/>
       <c r="B18" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="193"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="193"/>
+      <c r="J18" s="193"/>
+      <c r="K18" s="193"/>
+      <c r="L18" s="193"/>
+      <c r="M18" s="193"/>
+      <c r="N18" s="193"/>
+      <c r="O18" s="193"/>
+      <c r="P18" s="193"/>
+      <c r="Q18" s="193"/>
+      <c r="R18" s="193"/>
+      <c r="S18" s="193"/>
+      <c r="T18" s="193"/>
+      <c r="U18" s="193"/>
+      <c r="V18" s="193"/>
+      <c r="W18" s="193"/>
+      <c r="X18" s="193"/>
+      <c r="Y18" s="193"/>
+      <c r="Z18" s="193"/>
     </row>
     <row r="19" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A19" s="107"/>
+      <c r="A19" s="196"/>
       <c r="B19" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="98"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="98"/>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="98"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="98"/>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="193"/>
+      <c r="J19" s="193"/>
+      <c r="K19" s="193"/>
+      <c r="L19" s="193"/>
+      <c r="M19" s="193"/>
+      <c r="N19" s="193"/>
+      <c r="O19" s="193"/>
+      <c r="P19" s="193"/>
+      <c r="Q19" s="193"/>
+      <c r="R19" s="193"/>
+      <c r="S19" s="193"/>
+      <c r="T19" s="193"/>
+      <c r="U19" s="193"/>
+      <c r="V19" s="193"/>
+      <c r="W19" s="193"/>
+      <c r="X19" s="193"/>
+      <c r="Y19" s="193"/>
+      <c r="Z19" s="193"/>
     </row>
     <row r="20" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A20" s="107"/>
+      <c r="A20" s="196"/>
       <c r="B20" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
-      <c r="V20" s="98"/>
-      <c r="W20" s="98"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="98"/>
-      <c r="Z20" s="98"/>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="193"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="193"/>
+      <c r="J20" s="193"/>
+      <c r="K20" s="193"/>
+      <c r="L20" s="193"/>
+      <c r="M20" s="193"/>
+      <c r="N20" s="193"/>
+      <c r="O20" s="193"/>
+      <c r="P20" s="193"/>
+      <c r="Q20" s="193"/>
+      <c r="R20" s="193"/>
+      <c r="S20" s="193"/>
+      <c r="T20" s="193"/>
+      <c r="U20" s="193"/>
+      <c r="V20" s="193"/>
+      <c r="W20" s="193"/>
+      <c r="X20" s="193"/>
+      <c r="Y20" s="193"/>
+      <c r="Z20" s="193"/>
     </row>
     <row r="21" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A21" s="108"/>
+      <c r="A21" s="197"/>
       <c r="B21" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="98"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="F21" s="193"/>
+      <c r="G21" s="193"/>
+      <c r="H21" s="193"/>
+      <c r="I21" s="193"/>
+      <c r="J21" s="193"/>
+      <c r="K21" s="193"/>
+      <c r="L21" s="193"/>
+      <c r="M21" s="193"/>
+      <c r="N21" s="193"/>
+      <c r="O21" s="193"/>
+      <c r="P21" s="193"/>
+      <c r="Q21" s="193"/>
+      <c r="R21" s="193"/>
+      <c r="S21" s="193"/>
+      <c r="T21" s="193"/>
+      <c r="U21" s="193"/>
+      <c r="V21" s="193"/>
+      <c r="W21" s="193"/>
+      <c r="X21" s="193"/>
+      <c r="Y21" s="193"/>
+      <c r="Z21" s="193"/>
     </row>
     <row r="22" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
       <c r="A22" s="66">
@@ -5673,30 +5677,30 @@
       <c r="B22" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="193"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="193"/>
+      <c r="G22" s="193"/>
+      <c r="H22" s="193"/>
+      <c r="I22" s="193"/>
+      <c r="J22" s="193"/>
+      <c r="K22" s="193"/>
+      <c r="L22" s="193"/>
+      <c r="M22" s="193"/>
+      <c r="N22" s="193"/>
+      <c r="O22" s="193"/>
+      <c r="P22" s="193"/>
+      <c r="Q22" s="193"/>
+      <c r="R22" s="193"/>
+      <c r="S22" s="193"/>
+      <c r="T22" s="193"/>
+      <c r="U22" s="193"/>
+      <c r="V22" s="193"/>
+      <c r="W22" s="193"/>
+      <c r="X22" s="193"/>
+      <c r="Y22" s="193"/>
+      <c r="Z22" s="193"/>
     </row>
     <row r="23" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
       <c r="A23" s="66">
@@ -5705,30 +5709,30 @@
       <c r="B23" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="98"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="98"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="98"/>
-      <c r="V23" s="98"/>
-      <c r="W23" s="98"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="98"/>
-      <c r="Z23" s="98"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="193"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="193"/>
+      <c r="I23" s="193"/>
+      <c r="J23" s="193"/>
+      <c r="K23" s="193"/>
+      <c r="L23" s="193"/>
+      <c r="M23" s="193"/>
+      <c r="N23" s="193"/>
+      <c r="O23" s="193"/>
+      <c r="P23" s="193"/>
+      <c r="Q23" s="193"/>
+      <c r="R23" s="193"/>
+      <c r="S23" s="193"/>
+      <c r="T23" s="193"/>
+      <c r="U23" s="193"/>
+      <c r="V23" s="193"/>
+      <c r="W23" s="193"/>
+      <c r="X23" s="193"/>
+      <c r="Y23" s="193"/>
+      <c r="Z23" s="193"/>
     </row>
     <row r="24" spans="1:26" s="65" customFormat="1" ht="22.5" customHeight="1">
       <c r="A24" s="66">
@@ -5737,944 +5741,944 @@
       <c r="B24" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="98"/>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="98"/>
-      <c r="T24" s="98"/>
-      <c r="U24" s="98"/>
-      <c r="V24" s="98"/>
-      <c r="W24" s="98"/>
-      <c r="X24" s="98"/>
-      <c r="Y24" s="98"/>
-      <c r="Z24" s="98"/>
-    </row>
-    <row r="25" spans="1:26" s="65" customFormat="1" ht="20.65" customHeight="1">
+      <c r="C24" s="193"/>
+      <c r="D24" s="193"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="193"/>
+      <c r="G24" s="193"/>
+      <c r="H24" s="193"/>
+      <c r="I24" s="193"/>
+      <c r="J24" s="193"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193"/>
+      <c r="M24" s="193"/>
+      <c r="N24" s="193"/>
+      <c r="O24" s="193"/>
+      <c r="P24" s="193"/>
+      <c r="Q24" s="193"/>
+      <c r="R24" s="193"/>
+      <c r="S24" s="193"/>
+      <c r="T24" s="193"/>
+      <c r="U24" s="193"/>
+      <c r="V24" s="193"/>
+      <c r="W24" s="193"/>
+      <c r="X24" s="193"/>
+      <c r="Y24" s="193"/>
+      <c r="Z24" s="193"/>
+    </row>
+    <row r="25" spans="1:26" s="65" customFormat="1" ht="20.7" customHeight="1">
       <c r="A25" s="66">
         <v>6</v>
       </c>
       <c r="B25" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-      <c r="N25" s="98"/>
-      <c r="O25" s="98"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="98"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="98"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="98"/>
-      <c r="V25" s="98"/>
-      <c r="W25" s="98"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="98"/>
-      <c r="Z25" s="98"/>
-    </row>
-    <row r="26" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="193"/>
+      <c r="I25" s="193"/>
+      <c r="J25" s="193"/>
+      <c r="K25" s="193"/>
+      <c r="L25" s="193"/>
+      <c r="M25" s="193"/>
+      <c r="N25" s="193"/>
+      <c r="O25" s="193"/>
+      <c r="P25" s="193"/>
+      <c r="Q25" s="193"/>
+      <c r="R25" s="193"/>
+      <c r="S25" s="193"/>
+      <c r="T25" s="193"/>
+      <c r="U25" s="193"/>
+      <c r="V25" s="193"/>
+      <c r="W25" s="193"/>
+      <c r="X25" s="193"/>
+      <c r="Y25" s="193"/>
+      <c r="Z25" s="193"/>
+    </row>
+    <row r="26" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A26" s="8"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-    </row>
-    <row r="27" spans="1:26" s="7" customFormat="1" ht="15">
-      <c r="A27" s="215" t="s">
+      <c r="C26" s="175"/>
+      <c r="D26" s="175"/>
+      <c r="E26" s="175"/>
+      <c r="F26" s="175"/>
+    </row>
+    <row r="27" spans="1:26" s="7" customFormat="1" ht="15.6">
+      <c r="A27" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="215"/>
-      <c r="C27" s="215"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="215"/>
-      <c r="G27" s="215"/>
-      <c r="H27" s="215"/>
-      <c r="I27" s="215"/>
-      <c r="J27" s="215"/>
+      <c r="B27" s="194"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
     </row>
     <row r="28" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A28" s="205" t="s">
+      <c r="A28" s="182" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="206"/>
-      <c r="C28" s="211" t="s">
+      <c r="B28" s="183"/>
+      <c r="C28" s="189" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="211"/>
-      <c r="E28" s="211"/>
-      <c r="F28" s="211"/>
-      <c r="G28" s="212" t="s">
+      <c r="D28" s="189"/>
+      <c r="E28" s="189"/>
+      <c r="F28" s="189"/>
+      <c r="G28" s="190" t="s">
         <v>107</v>
       </c>
-      <c r="H28" s="213"/>
-      <c r="I28" s="213"/>
-      <c r="J28" s="214"/>
-      <c r="L28" s="96" t="s">
+      <c r="H28" s="191"/>
+      <c r="I28" s="191"/>
+      <c r="J28" s="192"/>
+      <c r="L28" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="M28" s="96"/>
+      <c r="M28" s="187"/>
     </row>
     <row r="29" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A29" s="205" t="s">
+      <c r="A29" s="182" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="206"/>
-      <c r="C29" s="210">
+      <c r="B29" s="183"/>
+      <c r="C29" s="188">
         <v>10</v>
       </c>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
-      <c r="G29" s="210">
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="188">
         <v>10</v>
       </c>
-      <c r="H29" s="210"/>
-      <c r="I29" s="210"/>
-      <c r="J29" s="210"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96"/>
+      <c r="H29" s="188"/>
+      <c r="I29" s="188"/>
+      <c r="J29" s="188"/>
+      <c r="L29" s="187"/>
+      <c r="M29" s="187"/>
     </row>
     <row r="30" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A30" s="205" t="s">
+      <c r="A30" s="182" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="206"/>
-      <c r="C30" s="210">
+      <c r="B30" s="183"/>
+      <c r="C30" s="188">
         <v>20</v>
       </c>
-      <c r="D30" s="210"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="210"/>
-      <c r="G30" s="210">
+      <c r="D30" s="188"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="188"/>
+      <c r="G30" s="188">
         <v>20</v>
       </c>
-      <c r="H30" s="210"/>
-      <c r="I30" s="210"/>
-      <c r="J30" s="210"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
+      <c r="H30" s="188"/>
+      <c r="I30" s="188"/>
+      <c r="J30" s="188"/>
+      <c r="L30" s="187"/>
+      <c r="M30" s="187"/>
     </row>
     <row r="31" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A31" s="205" t="s">
+      <c r="A31" s="182" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="210">
+      <c r="B31" s="183"/>
+      <c r="C31" s="188">
         <v>30</v>
       </c>
-      <c r="D31" s="210"/>
-      <c r="E31" s="210"/>
-      <c r="F31" s="210"/>
-      <c r="G31" s="210">
+      <c r="D31" s="188"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="188"/>
+      <c r="G31" s="188">
         <v>30</v>
       </c>
-      <c r="H31" s="210"/>
-      <c r="I31" s="210"/>
-      <c r="J31" s="210"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
+      <c r="H31" s="188"/>
+      <c r="I31" s="188"/>
+      <c r="J31" s="188"/>
+      <c r="L31" s="187"/>
+      <c r="M31" s="187"/>
     </row>
     <row r="32" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A32" s="205" t="s">
+      <c r="A32" s="182" t="s">
         <v>111</v>
       </c>
-      <c r="B32" s="206"/>
-      <c r="C32" s="207">
+      <c r="B32" s="183"/>
+      <c r="C32" s="184">
         <v>40</v>
       </c>
-      <c r="D32" s="208"/>
-      <c r="E32" s="208"/>
-      <c r="F32" s="209"/>
-      <c r="G32" s="207">
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="184">
         <v>40</v>
       </c>
-      <c r="H32" s="208"/>
-      <c r="I32" s="208"/>
-      <c r="J32" s="209"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="186"/>
+      <c r="L32" s="187"/>
+      <c r="M32" s="187"/>
     </row>
     <row r="33" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A33" s="205" t="s">
+      <c r="A33" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="206"/>
-      <c r="C33" s="210">
+      <c r="B33" s="183"/>
+      <c r="C33" s="188">
         <v>50</v>
       </c>
-      <c r="D33" s="210"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="210"/>
-      <c r="G33" s="210">
+      <c r="D33" s="188"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="188"/>
+      <c r="G33" s="188">
         <v>50</v>
       </c>
-      <c r="H33" s="210"/>
-      <c r="I33" s="210"/>
-      <c r="J33" s="210"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="188"/>
+      <c r="L33" s="187"/>
+      <c r="M33" s="187"/>
     </row>
     <row r="34" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A34" s="205" t="s">
+      <c r="A34" s="182" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="206"/>
-      <c r="C34" s="210">
+      <c r="B34" s="183"/>
+      <c r="C34" s="188">
         <v>100</v>
       </c>
-      <c r="D34" s="210"/>
-      <c r="E34" s="210"/>
-      <c r="F34" s="210"/>
-      <c r="G34" s="210">
+      <c r="D34" s="188"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188">
         <v>100</v>
       </c>
-      <c r="H34" s="210"/>
-      <c r="I34" s="210"/>
-      <c r="J34" s="210"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="188"/>
+      <c r="L34" s="187"/>
+      <c r="M34" s="187"/>
     </row>
     <row r="35" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A35" s="205" t="s">
+      <c r="A35" s="182" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="206"/>
-      <c r="C35" s="210">
+      <c r="B35" s="183"/>
+      <c r="C35" s="188">
         <v>200</v>
       </c>
-      <c r="D35" s="210"/>
-      <c r="E35" s="210"/>
-      <c r="F35" s="210"/>
-      <c r="G35" s="210">
+      <c r="D35" s="188"/>
+      <c r="E35" s="188"/>
+      <c r="F35" s="188"/>
+      <c r="G35" s="188">
         <v>200</v>
       </c>
-      <c r="H35" s="210"/>
-      <c r="I35" s="210"/>
-      <c r="J35" s="210"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
+      <c r="H35" s="188"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="188"/>
+      <c r="L35" s="187"/>
+      <c r="M35" s="187"/>
     </row>
     <row r="36" spans="1:26" s="69" customFormat="1" ht="15">
-      <c r="A36" s="205" t="s">
+      <c r="A36" s="182" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="206"/>
-      <c r="C36" s="207" t="s">
+      <c r="B36" s="183"/>
+      <c r="C36" s="184" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="208"/>
-      <c r="E36" s="208"/>
-      <c r="F36" s="208"/>
-      <c r="G36" s="208"/>
-      <c r="H36" s="208"/>
-      <c r="I36" s="208"/>
-      <c r="J36" s="209"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="96"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="186"/>
+      <c r="L36" s="187"/>
+      <c r="M36" s="187"/>
     </row>
     <row r="37" spans="1:26" s="69" customFormat="1" ht="15">
       <c r="A37" s="68"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="96"/>
+      <c r="L37" s="187"/>
+      <c r="M37" s="187"/>
     </row>
     <row r="38" spans="1:26" s="69" customFormat="1" ht="15">
       <c r="A38" s="68"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="96"/>
-    </row>
-    <row r="39" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L38" s="187"/>
+      <c r="M38" s="187"/>
+    </row>
+    <row r="39" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A39" s="8"/>
-      <c r="L39" s="97"/>
-      <c r="M39" s="97"/>
-    </row>
-    <row r="40" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L39" s="175"/>
+      <c r="M39" s="175"/>
+    </row>
+    <row r="40" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A40" s="8"/>
-      <c r="L40" s="97"/>
-      <c r="M40" s="97"/>
-    </row>
-    <row r="41" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L40" s="175"/>
+      <c r="M40" s="175"/>
+    </row>
+    <row r="41" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A41" s="8"/>
-      <c r="L41" s="97"/>
-      <c r="M41" s="97"/>
-    </row>
-    <row r="42" spans="1:26" s="69" customFormat="1" ht="19.25" customHeight="1">
+      <c r="L41" s="175"/>
+      <c r="M41" s="175"/>
+    </row>
+    <row r="42" spans="1:26" s="69" customFormat="1" ht="19.2" customHeight="1">
       <c r="A42" s="70" t="s">
         <v>117</v>
       </c>
       <c r="B42" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="199" t="s">
+      <c r="C42" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="200"/>
-      <c r="E42" s="200"/>
-      <c r="F42" s="200"/>
-      <c r="G42" s="200"/>
-      <c r="H42" s="200"/>
-      <c r="I42" s="200"/>
-      <c r="J42" s="200"/>
-      <c r="K42" s="200"/>
-      <c r="L42" s="200"/>
-      <c r="M42" s="200"/>
-      <c r="N42" s="201"/>
-      <c r="O42" s="202" t="s">
+      <c r="D42" s="177"/>
+      <c r="E42" s="177"/>
+      <c r="F42" s="177"/>
+      <c r="G42" s="177"/>
+      <c r="H42" s="177"/>
+      <c r="I42" s="177"/>
+      <c r="J42" s="177"/>
+      <c r="K42" s="177"/>
+      <c r="L42" s="177"/>
+      <c r="M42" s="177"/>
+      <c r="N42" s="178"/>
+      <c r="O42" s="179" t="s">
         <v>120</v>
       </c>
-      <c r="P42" s="203"/>
-      <c r="Q42" s="203"/>
-      <c r="R42" s="203"/>
-      <c r="S42" s="204"/>
-      <c r="T42" s="202" t="s">
+      <c r="P42" s="180"/>
+      <c r="Q42" s="180"/>
+      <c r="R42" s="180"/>
+      <c r="S42" s="181"/>
+      <c r="T42" s="179" t="s">
         <v>121</v>
       </c>
-      <c r="U42" s="203"/>
-      <c r="V42" s="203"/>
-      <c r="W42" s="204"/>
-      <c r="X42" s="203" t="s">
+      <c r="U42" s="180"/>
+      <c r="V42" s="180"/>
+      <c r="W42" s="181"/>
+      <c r="X42" s="180" t="s">
         <v>122</v>
       </c>
-      <c r="Y42" s="203"/>
-      <c r="Z42" s="204"/>
+      <c r="Y42" s="180"/>
+      <c r="Z42" s="181"/>
     </row>
     <row r="43" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A43" s="196" t="s">
+      <c r="A43" s="172" t="s">
         <v>123</v>
       </c>
       <c r="B43" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="C43" s="185" t="s">
+      <c r="C43" s="161" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="186"/>
-      <c r="E43" s="186"/>
-      <c r="F43" s="186"/>
-      <c r="G43" s="186"/>
-      <c r="H43" s="186"/>
-      <c r="I43" s="186"/>
-      <c r="J43" s="186"/>
-      <c r="K43" s="186"/>
-      <c r="L43" s="186"/>
-      <c r="M43" s="186"/>
-      <c r="N43" s="187"/>
-      <c r="O43" s="178" t="s">
+      <c r="D43" s="162"/>
+      <c r="E43" s="162"/>
+      <c r="F43" s="162"/>
+      <c r="G43" s="162"/>
+      <c r="H43" s="162"/>
+      <c r="I43" s="162"/>
+      <c r="J43" s="162"/>
+      <c r="K43" s="162"/>
+      <c r="L43" s="162"/>
+      <c r="M43" s="162"/>
+      <c r="N43" s="163"/>
+      <c r="O43" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P43" s="173"/>
-      <c r="Q43" s="173"/>
-      <c r="R43" s="173"/>
-      <c r="S43" s="174"/>
-      <c r="T43" s="178" t="s">
+      <c r="P43" s="149"/>
+      <c r="Q43" s="149"/>
+      <c r="R43" s="149"/>
+      <c r="S43" s="150"/>
+      <c r="T43" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="U43" s="173"/>
-      <c r="V43" s="173"/>
-      <c r="W43" s="174"/>
-      <c r="X43" s="178">
+      <c r="U43" s="149"/>
+      <c r="V43" s="149"/>
+      <c r="W43" s="150"/>
+      <c r="X43" s="154">
         <v>1</v>
       </c>
-      <c r="Y43" s="173"/>
-      <c r="Z43" s="174"/>
+      <c r="Y43" s="149"/>
+      <c r="Z43" s="150"/>
     </row>
     <row r="44" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A44" s="197"/>
+      <c r="A44" s="173"/>
       <c r="B44" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="185" t="s">
+      <c r="C44" s="161" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="186"/>
-      <c r="E44" s="186"/>
-      <c r="F44" s="186"/>
-      <c r="G44" s="186"/>
-      <c r="H44" s="186"/>
-      <c r="I44" s="186"/>
-      <c r="J44" s="186"/>
-      <c r="K44" s="186"/>
-      <c r="L44" s="186"/>
-      <c r="M44" s="186"/>
-      <c r="N44" s="187"/>
-      <c r="O44" s="178" t="s">
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="162"/>
+      <c r="K44" s="162"/>
+      <c r="L44" s="162"/>
+      <c r="M44" s="162"/>
+      <c r="N44" s="163"/>
+      <c r="O44" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P44" s="173"/>
-      <c r="Q44" s="173"/>
-      <c r="R44" s="173"/>
-      <c r="S44" s="174"/>
-      <c r="T44" s="178" t="s">
+      <c r="P44" s="149"/>
+      <c r="Q44" s="149"/>
+      <c r="R44" s="149"/>
+      <c r="S44" s="150"/>
+      <c r="T44" s="154" t="s">
         <v>130</v>
       </c>
-      <c r="U44" s="173"/>
-      <c r="V44" s="173"/>
-      <c r="W44" s="174"/>
-      <c r="X44" s="178">
+      <c r="U44" s="149"/>
+      <c r="V44" s="149"/>
+      <c r="W44" s="150"/>
+      <c r="X44" s="154">
         <v>1</v>
       </c>
-      <c r="Y44" s="173"/>
-      <c r="Z44" s="174"/>
+      <c r="Y44" s="149"/>
+      <c r="Z44" s="150"/>
     </row>
     <row r="45" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A45" s="197"/>
+      <c r="A45" s="173"/>
       <c r="B45" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="185" t="s">
+      <c r="C45" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="186"/>
-      <c r="E45" s="186"/>
-      <c r="F45" s="186"/>
-      <c r="G45" s="186"/>
-      <c r="H45" s="186"/>
-      <c r="I45" s="186"/>
-      <c r="J45" s="186"/>
-      <c r="K45" s="186"/>
-      <c r="L45" s="186"/>
-      <c r="M45" s="186"/>
-      <c r="N45" s="187"/>
-      <c r="O45" s="178" t="s">
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162"/>
+      <c r="K45" s="162"/>
+      <c r="L45" s="162"/>
+      <c r="M45" s="162"/>
+      <c r="N45" s="163"/>
+      <c r="O45" s="154" t="s">
         <v>133</v>
       </c>
-      <c r="P45" s="173"/>
-      <c r="Q45" s="173"/>
-      <c r="R45" s="173"/>
-      <c r="S45" s="174"/>
-      <c r="T45" s="178" t="s">
+      <c r="P45" s="149"/>
+      <c r="Q45" s="149"/>
+      <c r="R45" s="149"/>
+      <c r="S45" s="150"/>
+      <c r="T45" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="U45" s="173"/>
-      <c r="V45" s="173"/>
-      <c r="W45" s="174"/>
-      <c r="X45" s="178">
+      <c r="U45" s="149"/>
+      <c r="V45" s="149"/>
+      <c r="W45" s="150"/>
+      <c r="X45" s="154">
         <v>6</v>
       </c>
-      <c r="Y45" s="173"/>
-      <c r="Z45" s="174"/>
+      <c r="Y45" s="149"/>
+      <c r="Z45" s="150"/>
     </row>
     <row r="46" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="197"/>
+      <c r="A46" s="173"/>
       <c r="B46" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="C46" s="185" t="s">
+      <c r="C46" s="161" t="s">
         <v>136</v>
       </c>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="186"/>
-      <c r="G46" s="186"/>
-      <c r="H46" s="186"/>
-      <c r="I46" s="186"/>
-      <c r="J46" s="186"/>
-      <c r="K46" s="186"/>
-      <c r="L46" s="186"/>
-      <c r="M46" s="186"/>
-      <c r="N46" s="187"/>
-      <c r="O46" s="178" t="s">
+      <c r="D46" s="162"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="162"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="162"/>
+      <c r="K46" s="162"/>
+      <c r="L46" s="162"/>
+      <c r="M46" s="162"/>
+      <c r="N46" s="163"/>
+      <c r="O46" s="154" t="s">
         <v>137</v>
       </c>
-      <c r="P46" s="173"/>
-      <c r="Q46" s="173"/>
-      <c r="R46" s="173"/>
-      <c r="S46" s="174"/>
-      <c r="T46" s="178" t="s">
+      <c r="P46" s="149"/>
+      <c r="Q46" s="149"/>
+      <c r="R46" s="149"/>
+      <c r="S46" s="150"/>
+      <c r="T46" s="154" t="s">
         <v>138</v>
       </c>
-      <c r="U46" s="173"/>
-      <c r="V46" s="173"/>
-      <c r="W46" s="174"/>
-      <c r="X46" s="178">
+      <c r="U46" s="149"/>
+      <c r="V46" s="149"/>
+      <c r="W46" s="150"/>
+      <c r="X46" s="154">
         <v>6</v>
       </c>
-      <c r="Y46" s="173"/>
-      <c r="Z46" s="174"/>
+      <c r="Y46" s="149"/>
+      <c r="Z46" s="150"/>
     </row>
     <row r="47" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="198"/>
+      <c r="A47" s="174"/>
       <c r="B47" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="C47" s="185" t="s">
+      <c r="C47" s="161" t="s">
         <v>140</v>
       </c>
-      <c r="D47" s="186"/>
-      <c r="E47" s="186"/>
-      <c r="F47" s="186"/>
-      <c r="G47" s="186"/>
-      <c r="H47" s="186"/>
-      <c r="I47" s="186"/>
-      <c r="J47" s="186"/>
-      <c r="K47" s="186"/>
-      <c r="L47" s="186"/>
-      <c r="M47" s="186"/>
-      <c r="N47" s="187"/>
-      <c r="O47" s="178" t="s">
+      <c r="D47" s="162"/>
+      <c r="E47" s="162"/>
+      <c r="F47" s="162"/>
+      <c r="G47" s="162"/>
+      <c r="H47" s="162"/>
+      <c r="I47" s="162"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="162"/>
+      <c r="L47" s="162"/>
+      <c r="M47" s="162"/>
+      <c r="N47" s="163"/>
+      <c r="O47" s="154" t="s">
         <v>137</v>
       </c>
-      <c r="P47" s="173"/>
-      <c r="Q47" s="173"/>
-      <c r="R47" s="173"/>
-      <c r="S47" s="174"/>
-      <c r="T47" s="178" t="s">
+      <c r="P47" s="149"/>
+      <c r="Q47" s="149"/>
+      <c r="R47" s="149"/>
+      <c r="S47" s="150"/>
+      <c r="T47" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="U47" s="173"/>
-      <c r="V47" s="173"/>
-      <c r="W47" s="174"/>
-      <c r="X47" s="178">
+      <c r="U47" s="149"/>
+      <c r="V47" s="149"/>
+      <c r="W47" s="150"/>
+      <c r="X47" s="154">
         <v>6</v>
       </c>
-      <c r="Y47" s="173"/>
-      <c r="Z47" s="174"/>
+      <c r="Y47" s="149"/>
+      <c r="Z47" s="150"/>
     </row>
     <row r="48" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A48" s="190" t="s">
+      <c r="A48" s="166" t="s">
         <v>142</v>
       </c>
       <c r="B48" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="C48" s="185" t="s">
+      <c r="C48" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186"/>
-      <c r="G48" s="186"/>
-      <c r="H48" s="186"/>
-      <c r="I48" s="186"/>
-      <c r="J48" s="186"/>
-      <c r="K48" s="186"/>
-      <c r="L48" s="186"/>
-      <c r="M48" s="186"/>
-      <c r="N48" s="187"/>
-      <c r="O48" s="178" t="s">
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="162"/>
+      <c r="L48" s="162"/>
+      <c r="M48" s="162"/>
+      <c r="N48" s="163"/>
+      <c r="O48" s="154" t="s">
         <v>145</v>
       </c>
-      <c r="P48" s="173"/>
-      <c r="Q48" s="173"/>
-      <c r="R48" s="173"/>
-      <c r="S48" s="174"/>
-      <c r="T48" s="178" t="s">
+      <c r="P48" s="149"/>
+      <c r="Q48" s="149"/>
+      <c r="R48" s="149"/>
+      <c r="S48" s="150"/>
+      <c r="T48" s="154" t="s">
         <v>146</v>
       </c>
-      <c r="U48" s="173"/>
-      <c r="V48" s="173"/>
-      <c r="W48" s="174"/>
-      <c r="X48" s="178">
+      <c r="U48" s="149"/>
+      <c r="V48" s="149"/>
+      <c r="W48" s="150"/>
+      <c r="X48" s="154">
         <v>2</v>
       </c>
-      <c r="Y48" s="173"/>
-      <c r="Z48" s="174"/>
+      <c r="Y48" s="149"/>
+      <c r="Z48" s="150"/>
     </row>
     <row r="49" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="192"/>
+      <c r="A49" s="168"/>
       <c r="B49" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="185" t="s">
+      <c r="C49" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="186"/>
-      <c r="E49" s="186"/>
-      <c r="F49" s="186"/>
-      <c r="G49" s="186"/>
-      <c r="H49" s="186"/>
-      <c r="I49" s="186"/>
-      <c r="J49" s="186"/>
-      <c r="K49" s="186"/>
-      <c r="L49" s="186"/>
-      <c r="M49" s="186"/>
-      <c r="N49" s="187"/>
-      <c r="O49" s="178" t="s">
+      <c r="D49" s="162"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="162"/>
+      <c r="K49" s="162"/>
+      <c r="L49" s="162"/>
+      <c r="M49" s="162"/>
+      <c r="N49" s="163"/>
+      <c r="O49" s="154" t="s">
         <v>149</v>
       </c>
-      <c r="P49" s="173"/>
-      <c r="Q49" s="173"/>
-      <c r="R49" s="173"/>
-      <c r="S49" s="174"/>
-      <c r="T49" s="178" t="s">
+      <c r="P49" s="149"/>
+      <c r="Q49" s="149"/>
+      <c r="R49" s="149"/>
+      <c r="S49" s="150"/>
+      <c r="T49" s="154" t="s">
         <v>150</v>
       </c>
-      <c r="U49" s="173"/>
-      <c r="V49" s="173"/>
-      <c r="W49" s="174"/>
-      <c r="X49" s="178">
+      <c r="U49" s="149"/>
+      <c r="V49" s="149"/>
+      <c r="W49" s="150"/>
+      <c r="X49" s="154">
         <v>1</v>
       </c>
-      <c r="Y49" s="173"/>
-      <c r="Z49" s="174"/>
+      <c r="Y49" s="149"/>
+      <c r="Z49" s="150"/>
     </row>
     <row r="50" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="190" t="s">
+      <c r="A50" s="166" t="s">
         <v>151</v>
       </c>
       <c r="B50" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="C50" s="185" t="s">
+      <c r="C50" s="161" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="186"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="186"/>
-      <c r="H50" s="186"/>
-      <c r="I50" s="186"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="186"/>
-      <c r="M50" s="186"/>
-      <c r="N50" s="187"/>
-      <c r="O50" s="178" t="s">
+      <c r="D50" s="162"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="162"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="162"/>
+      <c r="K50" s="162"/>
+      <c r="L50" s="162"/>
+      <c r="M50" s="162"/>
+      <c r="N50" s="163"/>
+      <c r="O50" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P50" s="173"/>
-      <c r="Q50" s="173"/>
-      <c r="R50" s="173"/>
-      <c r="S50" s="174"/>
-      <c r="T50" s="178" t="s">
+      <c r="P50" s="149"/>
+      <c r="Q50" s="149"/>
+      <c r="R50" s="149"/>
+      <c r="S50" s="150"/>
+      <c r="T50" s="154" t="s">
         <v>154</v>
       </c>
-      <c r="U50" s="173"/>
-      <c r="V50" s="173"/>
-      <c r="W50" s="174"/>
-      <c r="X50" s="178">
+      <c r="U50" s="149"/>
+      <c r="V50" s="149"/>
+      <c r="W50" s="150"/>
+      <c r="X50" s="154">
         <v>1</v>
       </c>
-      <c r="Y50" s="173"/>
-      <c r="Z50" s="174"/>
+      <c r="Y50" s="149"/>
+      <c r="Z50" s="150"/>
     </row>
     <row r="51" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="191"/>
+      <c r="A51" s="167"/>
       <c r="B51" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C51" s="185" t="s">
+      <c r="C51" s="161" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="186"/>
-      <c r="E51" s="186"/>
-      <c r="F51" s="186"/>
-      <c r="G51" s="186"/>
-      <c r="H51" s="186"/>
-      <c r="I51" s="186"/>
-      <c r="J51" s="186"/>
-      <c r="K51" s="186"/>
-      <c r="L51" s="186"/>
-      <c r="M51" s="186"/>
-      <c r="N51" s="187"/>
-      <c r="O51" s="178" t="s">
+      <c r="D51" s="162"/>
+      <c r="E51" s="162"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="162"/>
+      <c r="I51" s="162"/>
+      <c r="J51" s="162"/>
+      <c r="K51" s="162"/>
+      <c r="L51" s="162"/>
+      <c r="M51" s="162"/>
+      <c r="N51" s="163"/>
+      <c r="O51" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P51" s="173"/>
-      <c r="Q51" s="173"/>
-      <c r="R51" s="173"/>
-      <c r="S51" s="174"/>
-      <c r="T51" s="178" t="s">
+      <c r="P51" s="149"/>
+      <c r="Q51" s="149"/>
+      <c r="R51" s="149"/>
+      <c r="S51" s="150"/>
+      <c r="T51" s="154" t="s">
         <v>157</v>
       </c>
-      <c r="U51" s="173"/>
-      <c r="V51" s="173"/>
-      <c r="W51" s="174"/>
-      <c r="X51" s="178">
+      <c r="U51" s="149"/>
+      <c r="V51" s="149"/>
+      <c r="W51" s="150"/>
+      <c r="X51" s="154">
         <v>4</v>
       </c>
-      <c r="Y51" s="173"/>
-      <c r="Z51" s="174"/>
+      <c r="Y51" s="149"/>
+      <c r="Z51" s="150"/>
     </row>
     <row r="52" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A52" s="191"/>
+      <c r="A52" s="167"/>
       <c r="B52" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="C52" s="185" t="s">
+      <c r="C52" s="161" t="s">
         <v>159</v>
       </c>
-      <c r="D52" s="186"/>
-      <c r="E52" s="186"/>
-      <c r="F52" s="186"/>
-      <c r="G52" s="186"/>
-      <c r="H52" s="186"/>
-      <c r="I52" s="186"/>
-      <c r="J52" s="186"/>
-      <c r="K52" s="186"/>
-      <c r="L52" s="186"/>
-      <c r="M52" s="186"/>
-      <c r="N52" s="187"/>
-      <c r="O52" s="178" t="s">
+      <c r="D52" s="162"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="162"/>
+      <c r="K52" s="162"/>
+      <c r="L52" s="162"/>
+      <c r="M52" s="162"/>
+      <c r="N52" s="163"/>
+      <c r="O52" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P52" s="173"/>
-      <c r="Q52" s="173"/>
-      <c r="R52" s="173"/>
-      <c r="S52" s="174"/>
-      <c r="T52" s="178" t="s">
+      <c r="P52" s="149"/>
+      <c r="Q52" s="149"/>
+      <c r="R52" s="149"/>
+      <c r="S52" s="150"/>
+      <c r="T52" s="154" t="s">
         <v>160</v>
       </c>
-      <c r="U52" s="173"/>
-      <c r="V52" s="173"/>
-      <c r="W52" s="174"/>
-      <c r="X52" s="178">
+      <c r="U52" s="149"/>
+      <c r="V52" s="149"/>
+      <c r="W52" s="150"/>
+      <c r="X52" s="154">
         <v>1</v>
       </c>
-      <c r="Y52" s="173"/>
-      <c r="Z52" s="174"/>
+      <c r="Y52" s="149"/>
+      <c r="Z52" s="150"/>
     </row>
     <row r="53" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A53" s="192"/>
+      <c r="A53" s="168"/>
       <c r="B53" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="C53" s="185" t="s">
+      <c r="C53" s="161" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="186"/>
-      <c r="E53" s="186"/>
-      <c r="F53" s="186"/>
-      <c r="G53" s="186"/>
-      <c r="H53" s="186"/>
-      <c r="I53" s="186"/>
-      <c r="J53" s="186"/>
-      <c r="K53" s="186"/>
-      <c r="L53" s="186"/>
-      <c r="M53" s="186"/>
-      <c r="N53" s="187"/>
-      <c r="O53" s="178" t="s">
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="162"/>
+      <c r="K53" s="162"/>
+      <c r="L53" s="162"/>
+      <c r="M53" s="162"/>
+      <c r="N53" s="163"/>
+      <c r="O53" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P53" s="173"/>
-      <c r="Q53" s="173"/>
-      <c r="R53" s="173"/>
-      <c r="S53" s="174"/>
-      <c r="T53" s="178" t="s">
+      <c r="P53" s="149"/>
+      <c r="Q53" s="149"/>
+      <c r="R53" s="149"/>
+      <c r="S53" s="150"/>
+      <c r="T53" s="154" t="s">
         <v>163</v>
       </c>
-      <c r="U53" s="173"/>
-      <c r="V53" s="173"/>
-      <c r="W53" s="174"/>
-      <c r="X53" s="178">
+      <c r="U53" s="149"/>
+      <c r="V53" s="149"/>
+      <c r="W53" s="150"/>
+      <c r="X53" s="154">
         <v>1</v>
       </c>
-      <c r="Y53" s="173"/>
-      <c r="Z53" s="174"/>
+      <c r="Y53" s="149"/>
+      <c r="Z53" s="150"/>
     </row>
     <row r="54" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A54" s="193" t="s">
+      <c r="A54" s="169" t="s">
         <v>164</v>
       </c>
       <c r="B54" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C54" s="185" t="s">
+      <c r="C54" s="161" t="s">
         <v>166</v>
       </c>
-      <c r="D54" s="186"/>
-      <c r="E54" s="186"/>
-      <c r="F54" s="186"/>
-      <c r="G54" s="186"/>
-      <c r="H54" s="186"/>
-      <c r="I54" s="186"/>
-      <c r="J54" s="186"/>
-      <c r="K54" s="186"/>
-      <c r="L54" s="186"/>
-      <c r="M54" s="186"/>
-      <c r="N54" s="187"/>
-      <c r="O54" s="178" t="s">
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="162"/>
+      <c r="K54" s="162"/>
+      <c r="L54" s="162"/>
+      <c r="M54" s="162"/>
+      <c r="N54" s="163"/>
+      <c r="O54" s="154" t="s">
         <v>167</v>
       </c>
-      <c r="P54" s="173"/>
-      <c r="Q54" s="173"/>
-      <c r="R54" s="173"/>
-      <c r="S54" s="174"/>
-      <c r="T54" s="178" t="s">
+      <c r="P54" s="149"/>
+      <c r="Q54" s="149"/>
+      <c r="R54" s="149"/>
+      <c r="S54" s="150"/>
+      <c r="T54" s="154" t="s">
         <v>168</v>
       </c>
-      <c r="U54" s="173"/>
-      <c r="V54" s="173"/>
-      <c r="W54" s="174"/>
-      <c r="X54" s="178">
+      <c r="U54" s="149"/>
+      <c r="V54" s="149"/>
+      <c r="W54" s="150"/>
+      <c r="X54" s="154">
         <v>1</v>
       </c>
-      <c r="Y54" s="173"/>
-      <c r="Z54" s="174"/>
+      <c r="Y54" s="149"/>
+      <c r="Z54" s="150"/>
     </row>
     <row r="55" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A55" s="194"/>
+      <c r="A55" s="170"/>
       <c r="B55" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="185" t="s">
+      <c r="C55" s="161" t="s">
         <v>170</v>
       </c>
-      <c r="D55" s="186"/>
-      <c r="E55" s="186"/>
-      <c r="F55" s="186"/>
-      <c r="G55" s="186"/>
-      <c r="H55" s="186"/>
-      <c r="I55" s="186"/>
-      <c r="J55" s="186"/>
-      <c r="K55" s="186"/>
-      <c r="L55" s="186"/>
-      <c r="M55" s="186"/>
-      <c r="N55" s="187"/>
-      <c r="O55" s="178" t="s">
+      <c r="D55" s="162"/>
+      <c r="E55" s="162"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="162"/>
+      <c r="K55" s="162"/>
+      <c r="L55" s="162"/>
+      <c r="M55" s="162"/>
+      <c r="N55" s="163"/>
+      <c r="O55" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P55" s="173"/>
-      <c r="Q55" s="173"/>
-      <c r="R55" s="173"/>
-      <c r="S55" s="174"/>
-      <c r="T55" s="178" t="s">
+      <c r="P55" s="149"/>
+      <c r="Q55" s="149"/>
+      <c r="R55" s="149"/>
+      <c r="S55" s="150"/>
+      <c r="T55" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="U55" s="173"/>
-      <c r="V55" s="173"/>
-      <c r="W55" s="174"/>
-      <c r="X55" s="178">
+      <c r="U55" s="149"/>
+      <c r="V55" s="149"/>
+      <c r="W55" s="150"/>
+      <c r="X55" s="154">
         <v>2</v>
       </c>
-      <c r="Y55" s="173"/>
-      <c r="Z55" s="174"/>
+      <c r="Y55" s="149"/>
+      <c r="Z55" s="150"/>
     </row>
     <row r="56" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A56" s="194"/>
+      <c r="A56" s="170"/>
       <c r="B56" s="70" t="s">
         <v>171</v>
       </c>
-      <c r="C56" s="185" t="s">
+      <c r="C56" s="161" t="s">
         <v>172</v>
       </c>
-      <c r="D56" s="186"/>
-      <c r="E56" s="186"/>
-      <c r="F56" s="186"/>
-      <c r="G56" s="186"/>
-      <c r="H56" s="186"/>
-      <c r="I56" s="186"/>
-      <c r="J56" s="186"/>
-      <c r="K56" s="186"/>
-      <c r="L56" s="186"/>
-      <c r="M56" s="186"/>
-      <c r="N56" s="187"/>
-      <c r="O56" s="178" t="s">
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="162"/>
+      <c r="K56" s="162"/>
+      <c r="L56" s="162"/>
+      <c r="M56" s="162"/>
+      <c r="N56" s="163"/>
+      <c r="O56" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P56" s="173"/>
-      <c r="Q56" s="173"/>
-      <c r="R56" s="173"/>
-      <c r="S56" s="174"/>
-      <c r="T56" s="178" t="s">
+      <c r="P56" s="149"/>
+      <c r="Q56" s="149"/>
+      <c r="R56" s="149"/>
+      <c r="S56" s="150"/>
+      <c r="T56" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="U56" s="173"/>
-      <c r="V56" s="173"/>
-      <c r="W56" s="174"/>
-      <c r="X56" s="178">
+      <c r="U56" s="149"/>
+      <c r="V56" s="149"/>
+      <c r="W56" s="150"/>
+      <c r="X56" s="154">
         <v>2</v>
       </c>
-      <c r="Y56" s="173"/>
-      <c r="Z56" s="174"/>
+      <c r="Y56" s="149"/>
+      <c r="Z56" s="150"/>
     </row>
     <row r="57" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A57" s="194"/>
+      <c r="A57" s="170"/>
       <c r="B57" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="C57" s="185" t="s">
+      <c r="C57" s="161" t="s">
         <v>175</v>
       </c>
-      <c r="D57" s="186"/>
-      <c r="E57" s="186"/>
-      <c r="F57" s="186"/>
-      <c r="G57" s="186"/>
-      <c r="H57" s="186"/>
-      <c r="I57" s="186"/>
-      <c r="J57" s="186"/>
-      <c r="K57" s="186"/>
-      <c r="L57" s="186"/>
-      <c r="M57" s="186"/>
-      <c r="N57" s="187"/>
-      <c r="O57" s="178" t="s">
+      <c r="D57" s="162"/>
+      <c r="E57" s="162"/>
+      <c r="F57" s="162"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="162"/>
+      <c r="I57" s="162"/>
+      <c r="J57" s="162"/>
+      <c r="K57" s="162"/>
+      <c r="L57" s="162"/>
+      <c r="M57" s="162"/>
+      <c r="N57" s="163"/>
+      <c r="O57" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P57" s="173"/>
-      <c r="Q57" s="173"/>
-      <c r="R57" s="173"/>
-      <c r="S57" s="174"/>
-      <c r="T57" s="178" t="s">
+      <c r="P57" s="149"/>
+      <c r="Q57" s="149"/>
+      <c r="R57" s="149"/>
+      <c r="S57" s="150"/>
+      <c r="T57" s="154" t="s">
         <v>176</v>
       </c>
-      <c r="U57" s="173"/>
-      <c r="V57" s="173"/>
-      <c r="W57" s="174"/>
-      <c r="X57" s="178">
+      <c r="U57" s="149"/>
+      <c r="V57" s="149"/>
+      <c r="W57" s="150"/>
+      <c r="X57" s="154">
         <v>2</v>
       </c>
-      <c r="Y57" s="173"/>
-      <c r="Z57" s="174"/>
+      <c r="Y57" s="149"/>
+      <c r="Z57" s="150"/>
     </row>
     <row r="58" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A58" s="195"/>
+      <c r="A58" s="171"/>
       <c r="B58" s="70" t="s">
         <v>177</v>
       </c>
-      <c r="C58" s="185" t="s">
+      <c r="C58" s="161" t="s">
         <v>178</v>
       </c>
-      <c r="D58" s="186"/>
-      <c r="E58" s="186"/>
-      <c r="F58" s="186"/>
-      <c r="G58" s="186"/>
-      <c r="H58" s="186"/>
-      <c r="I58" s="186"/>
-      <c r="J58" s="186"/>
-      <c r="K58" s="186"/>
-      <c r="L58" s="186"/>
-      <c r="M58" s="186"/>
-      <c r="N58" s="187"/>
-      <c r="O58" s="178" t="s">
+      <c r="D58" s="162"/>
+      <c r="E58" s="162"/>
+      <c r="F58" s="162"/>
+      <c r="G58" s="162"/>
+      <c r="H58" s="162"/>
+      <c r="I58" s="162"/>
+      <c r="J58" s="162"/>
+      <c r="K58" s="162"/>
+      <c r="L58" s="162"/>
+      <c r="M58" s="162"/>
+      <c r="N58" s="163"/>
+      <c r="O58" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P58" s="173"/>
-      <c r="Q58" s="173"/>
-      <c r="R58" s="173"/>
-      <c r="S58" s="174"/>
-      <c r="T58" s="178" t="s">
+      <c r="P58" s="149"/>
+      <c r="Q58" s="149"/>
+      <c r="R58" s="149"/>
+      <c r="S58" s="150"/>
+      <c r="T58" s="154" t="s">
         <v>179</v>
       </c>
-      <c r="U58" s="173"/>
-      <c r="V58" s="173"/>
-      <c r="W58" s="174"/>
-      <c r="X58" s="178">
+      <c r="U58" s="149"/>
+      <c r="V58" s="149"/>
+      <c r="W58" s="150"/>
+      <c r="X58" s="154">
         <v>22</v>
       </c>
-      <c r="Y58" s="173"/>
-      <c r="Z58" s="174"/>
+      <c r="Y58" s="149"/>
+      <c r="Z58" s="150"/>
     </row>
     <row r="59" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A59" s="72" t="s">
@@ -6683,38 +6687,38 @@
       <c r="B59" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="C59" s="185" t="s">
+      <c r="C59" s="161" t="s">
         <v>182</v>
       </c>
-      <c r="D59" s="186"/>
-      <c r="E59" s="186"/>
-      <c r="F59" s="186"/>
-      <c r="G59" s="186"/>
-      <c r="H59" s="186"/>
-      <c r="I59" s="186"/>
-      <c r="J59" s="186"/>
-      <c r="K59" s="186"/>
-      <c r="L59" s="186"/>
-      <c r="M59" s="186"/>
-      <c r="N59" s="187"/>
-      <c r="O59" s="178" t="s">
+      <c r="D59" s="162"/>
+      <c r="E59" s="162"/>
+      <c r="F59" s="162"/>
+      <c r="G59" s="162"/>
+      <c r="H59" s="162"/>
+      <c r="I59" s="162"/>
+      <c r="J59" s="162"/>
+      <c r="K59" s="162"/>
+      <c r="L59" s="162"/>
+      <c r="M59" s="162"/>
+      <c r="N59" s="163"/>
+      <c r="O59" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P59" s="173"/>
-      <c r="Q59" s="173"/>
-      <c r="R59" s="173"/>
-      <c r="S59" s="174"/>
-      <c r="T59" s="178" t="s">
+      <c r="P59" s="149"/>
+      <c r="Q59" s="149"/>
+      <c r="R59" s="149"/>
+      <c r="S59" s="150"/>
+      <c r="T59" s="154" t="s">
         <v>183</v>
       </c>
-      <c r="U59" s="173"/>
-      <c r="V59" s="173"/>
-      <c r="W59" s="174"/>
-      <c r="X59" s="178">
+      <c r="U59" s="149"/>
+      <c r="V59" s="149"/>
+      <c r="W59" s="150"/>
+      <c r="X59" s="154">
         <v>8</v>
       </c>
-      <c r="Y59" s="173"/>
-      <c r="Z59" s="174"/>
+      <c r="Y59" s="149"/>
+      <c r="Z59" s="150"/>
     </row>
     <row r="60" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A60" s="72" t="s">
@@ -6723,116 +6727,116 @@
       <c r="B60" s="70" t="s">
         <v>185</v>
       </c>
-      <c r="C60" s="185" t="s">
+      <c r="C60" s="161" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="186"/>
-      <c r="E60" s="186"/>
-      <c r="F60" s="186"/>
-      <c r="G60" s="186"/>
-      <c r="H60" s="186"/>
-      <c r="I60" s="186"/>
-      <c r="J60" s="186"/>
-      <c r="K60" s="186"/>
-      <c r="L60" s="186"/>
-      <c r="M60" s="186"/>
-      <c r="N60" s="187"/>
-      <c r="O60" s="178" t="s">
+      <c r="D60" s="162"/>
+      <c r="E60" s="162"/>
+      <c r="F60" s="162"/>
+      <c r="G60" s="162"/>
+      <c r="H60" s="162"/>
+      <c r="I60" s="162"/>
+      <c r="J60" s="162"/>
+      <c r="K60" s="162"/>
+      <c r="L60" s="162"/>
+      <c r="M60" s="162"/>
+      <c r="N60" s="163"/>
+      <c r="O60" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P60" s="173"/>
-      <c r="Q60" s="173"/>
-      <c r="R60" s="173"/>
-      <c r="S60" s="174"/>
-      <c r="T60" s="178" t="s">
+      <c r="P60" s="149"/>
+      <c r="Q60" s="149"/>
+      <c r="R60" s="149"/>
+      <c r="S60" s="150"/>
+      <c r="T60" s="154" t="s">
         <v>186</v>
       </c>
-      <c r="U60" s="173"/>
-      <c r="V60" s="173"/>
-      <c r="W60" s="174"/>
-      <c r="X60" s="178">
+      <c r="U60" s="149"/>
+      <c r="V60" s="149"/>
+      <c r="W60" s="150"/>
+      <c r="X60" s="154">
         <v>1</v>
       </c>
-      <c r="Y60" s="173"/>
-      <c r="Z60" s="174"/>
+      <c r="Y60" s="149"/>
+      <c r="Z60" s="150"/>
     </row>
     <row r="61" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A61" s="188" t="s">
+      <c r="A61" s="164" t="s">
         <v>187</v>
       </c>
       <c r="B61" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="C61" s="185" t="s">
+      <c r="C61" s="161" t="s">
         <v>170</v>
       </c>
-      <c r="D61" s="186"/>
-      <c r="E61" s="186"/>
-      <c r="F61" s="186"/>
-      <c r="G61" s="186"/>
-      <c r="H61" s="186"/>
-      <c r="I61" s="186"/>
-      <c r="J61" s="186"/>
-      <c r="K61" s="186"/>
-      <c r="L61" s="186"/>
-      <c r="M61" s="186"/>
-      <c r="N61" s="187"/>
-      <c r="O61" s="178" t="s">
+      <c r="D61" s="162"/>
+      <c r="E61" s="162"/>
+      <c r="F61" s="162"/>
+      <c r="G61" s="162"/>
+      <c r="H61" s="162"/>
+      <c r="I61" s="162"/>
+      <c r="J61" s="162"/>
+      <c r="K61" s="162"/>
+      <c r="L61" s="162"/>
+      <c r="M61" s="162"/>
+      <c r="N61" s="163"/>
+      <c r="O61" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P61" s="173"/>
-      <c r="Q61" s="173"/>
-      <c r="R61" s="173"/>
-      <c r="S61" s="174"/>
-      <c r="T61" s="178" t="s">
+      <c r="P61" s="149"/>
+      <c r="Q61" s="149"/>
+      <c r="R61" s="149"/>
+      <c r="S61" s="150"/>
+      <c r="T61" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="U61" s="173"/>
-      <c r="V61" s="173"/>
-      <c r="W61" s="174"/>
-      <c r="X61" s="178">
+      <c r="U61" s="149"/>
+      <c r="V61" s="149"/>
+      <c r="W61" s="150"/>
+      <c r="X61" s="154">
         <v>2</v>
       </c>
-      <c r="Y61" s="173"/>
-      <c r="Z61" s="174"/>
+      <c r="Y61" s="149"/>
+      <c r="Z61" s="150"/>
     </row>
     <row r="62" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A62" s="189"/>
+      <c r="A62" s="165"/>
       <c r="B62" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="185" t="s">
+      <c r="C62" s="161" t="s">
         <v>190</v>
       </c>
-      <c r="D62" s="186"/>
-      <c r="E62" s="186"/>
-      <c r="F62" s="186"/>
-      <c r="G62" s="186"/>
-      <c r="H62" s="186"/>
-      <c r="I62" s="186"/>
-      <c r="J62" s="186"/>
-      <c r="K62" s="186"/>
-      <c r="L62" s="186"/>
-      <c r="M62" s="186"/>
-      <c r="N62" s="187"/>
-      <c r="O62" s="178" t="s">
+      <c r="D62" s="162"/>
+      <c r="E62" s="162"/>
+      <c r="F62" s="162"/>
+      <c r="G62" s="162"/>
+      <c r="H62" s="162"/>
+      <c r="I62" s="162"/>
+      <c r="J62" s="162"/>
+      <c r="K62" s="162"/>
+      <c r="L62" s="162"/>
+      <c r="M62" s="162"/>
+      <c r="N62" s="163"/>
+      <c r="O62" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="P62" s="173"/>
-      <c r="Q62" s="173"/>
-      <c r="R62" s="173"/>
-      <c r="S62" s="174"/>
-      <c r="T62" s="178" t="s">
+      <c r="P62" s="149"/>
+      <c r="Q62" s="149"/>
+      <c r="R62" s="149"/>
+      <c r="S62" s="150"/>
+      <c r="T62" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="U62" s="173"/>
-      <c r="V62" s="173"/>
-      <c r="W62" s="174"/>
-      <c r="X62" s="178">
+      <c r="U62" s="149"/>
+      <c r="V62" s="149"/>
+      <c r="W62" s="150"/>
+      <c r="X62" s="154">
         <v>1</v>
       </c>
-      <c r="Y62" s="173"/>
-      <c r="Z62" s="174"/>
+      <c r="Y62" s="149"/>
+      <c r="Z62" s="150"/>
     </row>
     <row r="63" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A63" s="72" t="s">
@@ -6841,38 +6845,38 @@
       <c r="B63" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="C63" s="185" t="s">
+      <c r="C63" s="161" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="186"/>
-      <c r="E63" s="186"/>
-      <c r="F63" s="186"/>
-      <c r="G63" s="186"/>
-      <c r="H63" s="186"/>
-      <c r="I63" s="186"/>
-      <c r="J63" s="186"/>
-      <c r="K63" s="186"/>
-      <c r="L63" s="186"/>
-      <c r="M63" s="186"/>
-      <c r="N63" s="187"/>
-      <c r="O63" s="178" t="s">
+      <c r="D63" s="162"/>
+      <c r="E63" s="162"/>
+      <c r="F63" s="162"/>
+      <c r="G63" s="162"/>
+      <c r="H63" s="162"/>
+      <c r="I63" s="162"/>
+      <c r="J63" s="162"/>
+      <c r="K63" s="162"/>
+      <c r="L63" s="162"/>
+      <c r="M63" s="162"/>
+      <c r="N63" s="163"/>
+      <c r="O63" s="154" t="s">
         <v>137</v>
       </c>
-      <c r="P63" s="173"/>
-      <c r="Q63" s="173"/>
-      <c r="R63" s="173"/>
-      <c r="S63" s="174"/>
-      <c r="T63" s="178" t="s">
+      <c r="P63" s="149"/>
+      <c r="Q63" s="149"/>
+      <c r="R63" s="149"/>
+      <c r="S63" s="150"/>
+      <c r="T63" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="U63" s="173"/>
-      <c r="V63" s="173"/>
-      <c r="W63" s="174"/>
-      <c r="X63" s="178">
+      <c r="U63" s="149"/>
+      <c r="V63" s="149"/>
+      <c r="W63" s="150"/>
+      <c r="X63" s="154">
         <v>1</v>
       </c>
-      <c r="Y63" s="173"/>
-      <c r="Z63" s="174"/>
+      <c r="Y63" s="149"/>
+      <c r="Z63" s="150"/>
     </row>
     <row r="64" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A64" s="72" t="s">
@@ -6881,38 +6885,38 @@
       <c r="B64" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="185" t="s">
+      <c r="C64" s="161" t="s">
         <v>166</v>
       </c>
-      <c r="D64" s="186"/>
-      <c r="E64" s="186"/>
-      <c r="F64" s="186"/>
-      <c r="G64" s="186"/>
-      <c r="H64" s="186"/>
-      <c r="I64" s="186"/>
-      <c r="J64" s="186"/>
-      <c r="K64" s="186"/>
-      <c r="L64" s="186"/>
-      <c r="M64" s="186"/>
-      <c r="N64" s="187"/>
-      <c r="O64" s="178" t="s">
+      <c r="D64" s="162"/>
+      <c r="E64" s="162"/>
+      <c r="F64" s="162"/>
+      <c r="G64" s="162"/>
+      <c r="H64" s="162"/>
+      <c r="I64" s="162"/>
+      <c r="J64" s="162"/>
+      <c r="K64" s="162"/>
+      <c r="L64" s="162"/>
+      <c r="M64" s="162"/>
+      <c r="N64" s="163"/>
+      <c r="O64" s="154" t="s">
         <v>167</v>
       </c>
-      <c r="P64" s="173"/>
-      <c r="Q64" s="173"/>
-      <c r="R64" s="173"/>
-      <c r="S64" s="174"/>
-      <c r="T64" s="178" t="s">
+      <c r="P64" s="149"/>
+      <c r="Q64" s="149"/>
+      <c r="R64" s="149"/>
+      <c r="S64" s="150"/>
+      <c r="T64" s="154" t="s">
         <v>168</v>
       </c>
-      <c r="U64" s="173"/>
-      <c r="V64" s="173"/>
-      <c r="W64" s="174"/>
-      <c r="X64" s="178">
+      <c r="U64" s="149"/>
+      <c r="V64" s="149"/>
+      <c r="W64" s="150"/>
+      <c r="X64" s="154">
         <v>1</v>
       </c>
-      <c r="Y64" s="173"/>
-      <c r="Z64" s="174"/>
+      <c r="Y64" s="149"/>
+      <c r="Z64" s="150"/>
     </row>
     <row r="65" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A65" s="72" t="s">
@@ -6921,38 +6925,38 @@
       <c r="B65" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="C65" s="185" t="s">
+      <c r="C65" s="161" t="s">
         <v>125</v>
       </c>
-      <c r="D65" s="186"/>
-      <c r="E65" s="186"/>
-      <c r="F65" s="186"/>
-      <c r="G65" s="186"/>
-      <c r="H65" s="186"/>
-      <c r="I65" s="186"/>
-      <c r="J65" s="186"/>
-      <c r="K65" s="186"/>
-      <c r="L65" s="186"/>
-      <c r="M65" s="186"/>
-      <c r="N65" s="187"/>
-      <c r="O65" s="178" t="s">
+      <c r="D65" s="162"/>
+      <c r="E65" s="162"/>
+      <c r="F65" s="162"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="162"/>
+      <c r="I65" s="162"/>
+      <c r="J65" s="162"/>
+      <c r="K65" s="162"/>
+      <c r="L65" s="162"/>
+      <c r="M65" s="162"/>
+      <c r="N65" s="163"/>
+      <c r="O65" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P65" s="173"/>
-      <c r="Q65" s="173"/>
-      <c r="R65" s="173"/>
-      <c r="S65" s="174"/>
-      <c r="T65" s="178" t="s">
+      <c r="P65" s="149"/>
+      <c r="Q65" s="149"/>
+      <c r="R65" s="149"/>
+      <c r="S65" s="150"/>
+      <c r="T65" s="154" t="s">
         <v>197</v>
       </c>
-      <c r="U65" s="173"/>
-      <c r="V65" s="173"/>
-      <c r="W65" s="174"/>
-      <c r="X65" s="178">
+      <c r="U65" s="149"/>
+      <c r="V65" s="149"/>
+      <c r="W65" s="150"/>
+      <c r="X65" s="154">
         <v>1</v>
       </c>
-      <c r="Y65" s="173"/>
-      <c r="Z65" s="174"/>
+      <c r="Y65" s="149"/>
+      <c r="Z65" s="150"/>
     </row>
     <row r="66" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A66" s="72" t="s">
@@ -6961,38 +6965,38 @@
       <c r="B66" s="70" t="s">
         <v>199</v>
       </c>
-      <c r="C66" s="185" t="s">
+      <c r="C66" s="161" t="s">
         <v>159</v>
       </c>
-      <c r="D66" s="186"/>
-      <c r="E66" s="186"/>
-      <c r="F66" s="186"/>
-      <c r="G66" s="186"/>
-      <c r="H66" s="186"/>
-      <c r="I66" s="186"/>
-      <c r="J66" s="186"/>
-      <c r="K66" s="186"/>
-      <c r="L66" s="186"/>
-      <c r="M66" s="186"/>
-      <c r="N66" s="187"/>
-      <c r="O66" s="178" t="s">
+      <c r="D66" s="162"/>
+      <c r="E66" s="162"/>
+      <c r="F66" s="162"/>
+      <c r="G66" s="162"/>
+      <c r="H66" s="162"/>
+      <c r="I66" s="162"/>
+      <c r="J66" s="162"/>
+      <c r="K66" s="162"/>
+      <c r="L66" s="162"/>
+      <c r="M66" s="162"/>
+      <c r="N66" s="163"/>
+      <c r="O66" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="P66" s="173"/>
-      <c r="Q66" s="173"/>
-      <c r="R66" s="173"/>
-      <c r="S66" s="174"/>
-      <c r="T66" s="178" t="s">
+      <c r="P66" s="149"/>
+      <c r="Q66" s="149"/>
+      <c r="R66" s="149"/>
+      <c r="S66" s="150"/>
+      <c r="T66" s="154" t="s">
         <v>160</v>
       </c>
-      <c r="U66" s="173"/>
-      <c r="V66" s="173"/>
-      <c r="W66" s="174"/>
-      <c r="X66" s="178">
+      <c r="U66" s="149"/>
+      <c r="V66" s="149"/>
+      <c r="W66" s="150"/>
+      <c r="X66" s="154">
         <v>1</v>
       </c>
-      <c r="Y66" s="173"/>
-      <c r="Z66" s="174"/>
+      <c r="Y66" s="149"/>
+      <c r="Z66" s="150"/>
     </row>
     <row r="67" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A67" s="72" t="s">
@@ -7001,38 +7005,38 @@
       <c r="B67" s="70" t="s">
         <v>201</v>
       </c>
-      <c r="C67" s="185" t="s">
+      <c r="C67" s="161" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="186"/>
-      <c r="E67" s="186"/>
-      <c r="F67" s="186"/>
-      <c r="G67" s="186"/>
-      <c r="H67" s="186"/>
-      <c r="I67" s="186"/>
-      <c r="J67" s="186"/>
-      <c r="K67" s="186"/>
-      <c r="L67" s="186"/>
-      <c r="M67" s="186"/>
-      <c r="N67" s="187"/>
-      <c r="O67" s="178" t="s">
+      <c r="D67" s="162"/>
+      <c r="E67" s="162"/>
+      <c r="F67" s="162"/>
+      <c r="G67" s="162"/>
+      <c r="H67" s="162"/>
+      <c r="I67" s="162"/>
+      <c r="J67" s="162"/>
+      <c r="K67" s="162"/>
+      <c r="L67" s="162"/>
+      <c r="M67" s="162"/>
+      <c r="N67" s="163"/>
+      <c r="O67" s="154" t="s">
         <v>137</v>
       </c>
-      <c r="P67" s="173"/>
-      <c r="Q67" s="173"/>
-      <c r="R67" s="173"/>
-      <c r="S67" s="174"/>
-      <c r="T67" s="178" t="s">
+      <c r="P67" s="149"/>
+      <c r="Q67" s="149"/>
+      <c r="R67" s="149"/>
+      <c r="S67" s="150"/>
+      <c r="T67" s="154" t="s">
         <v>138</v>
       </c>
-      <c r="U67" s="173"/>
-      <c r="V67" s="173"/>
-      <c r="W67" s="174"/>
-      <c r="X67" s="178">
+      <c r="U67" s="149"/>
+      <c r="V67" s="149"/>
+      <c r="W67" s="150"/>
+      <c r="X67" s="154">
         <v>6</v>
       </c>
-      <c r="Y67" s="173"/>
-      <c r="Z67" s="174"/>
+      <c r="Y67" s="149"/>
+      <c r="Z67" s="150"/>
     </row>
     <row r="68" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A68" s="70">
@@ -7041,38 +7045,38 @@
       <c r="B68" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="C68" s="172" t="s">
+      <c r="C68" s="148" t="s">
         <v>204</v>
       </c>
-      <c r="D68" s="183"/>
-      <c r="E68" s="183"/>
-      <c r="F68" s="183"/>
-      <c r="G68" s="183"/>
-      <c r="H68" s="183"/>
-      <c r="I68" s="183"/>
-      <c r="J68" s="183"/>
-      <c r="K68" s="183"/>
-      <c r="L68" s="183"/>
-      <c r="M68" s="183"/>
-      <c r="N68" s="184"/>
-      <c r="O68" s="175" t="s">
+      <c r="D68" s="159"/>
+      <c r="E68" s="159"/>
+      <c r="F68" s="159"/>
+      <c r="G68" s="159"/>
+      <c r="H68" s="159"/>
+      <c r="I68" s="159"/>
+      <c r="J68" s="159"/>
+      <c r="K68" s="159"/>
+      <c r="L68" s="159"/>
+      <c r="M68" s="159"/>
+      <c r="N68" s="160"/>
+      <c r="O68" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="P68" s="176"/>
-      <c r="Q68" s="176"/>
-      <c r="R68" s="176"/>
-      <c r="S68" s="177"/>
-      <c r="T68" s="178" t="s">
+      <c r="P68" s="152"/>
+      <c r="Q68" s="152"/>
+      <c r="R68" s="152"/>
+      <c r="S68" s="153"/>
+      <c r="T68" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="U68" s="173"/>
-      <c r="V68" s="173"/>
-      <c r="W68" s="174"/>
-      <c r="X68" s="178">
+      <c r="U68" s="149"/>
+      <c r="V68" s="149"/>
+      <c r="W68" s="150"/>
+      <c r="X68" s="154">
         <v>1</v>
       </c>
-      <c r="Y68" s="173"/>
-      <c r="Z68" s="174"/>
+      <c r="Y68" s="149"/>
+      <c r="Z68" s="150"/>
     </row>
     <row r="69" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A69" s="70" t="s">
@@ -7081,38 +7085,38 @@
       <c r="B69" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="C69" s="172" t="s">
+      <c r="C69" s="148" t="s">
         <v>206</v>
       </c>
-      <c r="D69" s="183"/>
-      <c r="E69" s="183"/>
-      <c r="F69" s="183"/>
-      <c r="G69" s="183"/>
-      <c r="H69" s="183"/>
-      <c r="I69" s="183"/>
-      <c r="J69" s="183"/>
-      <c r="K69" s="183"/>
-      <c r="L69" s="183"/>
-      <c r="M69" s="183"/>
-      <c r="N69" s="184"/>
-      <c r="O69" s="175" t="s">
+      <c r="D69" s="159"/>
+      <c r="E69" s="159"/>
+      <c r="F69" s="159"/>
+      <c r="G69" s="159"/>
+      <c r="H69" s="159"/>
+      <c r="I69" s="159"/>
+      <c r="J69" s="159"/>
+      <c r="K69" s="159"/>
+      <c r="L69" s="159"/>
+      <c r="M69" s="159"/>
+      <c r="N69" s="160"/>
+      <c r="O69" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="P69" s="176"/>
-      <c r="Q69" s="176"/>
-      <c r="R69" s="176"/>
-      <c r="S69" s="177"/>
-      <c r="T69" s="178" t="s">
+      <c r="P69" s="152"/>
+      <c r="Q69" s="152"/>
+      <c r="R69" s="152"/>
+      <c r="S69" s="153"/>
+      <c r="T69" s="154" t="s">
         <v>130</v>
       </c>
-      <c r="U69" s="173"/>
-      <c r="V69" s="173"/>
-      <c r="W69" s="174"/>
-      <c r="X69" s="178">
+      <c r="U69" s="149"/>
+      <c r="V69" s="149"/>
+      <c r="W69" s="150"/>
+      <c r="X69" s="154">
         <v>1</v>
       </c>
-      <c r="Y69" s="173"/>
-      <c r="Z69" s="174"/>
+      <c r="Y69" s="149"/>
+      <c r="Z69" s="150"/>
     </row>
     <row r="70" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A70" s="70" t="s">
@@ -7121,38 +7125,38 @@
       <c r="B70" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="C70" s="172" t="s">
+      <c r="C70" s="148" t="s">
         <v>208</v>
       </c>
-      <c r="D70" s="183"/>
-      <c r="E70" s="183"/>
-      <c r="F70" s="183"/>
-      <c r="G70" s="183"/>
-      <c r="H70" s="183"/>
-      <c r="I70" s="183"/>
-      <c r="J70" s="183"/>
-      <c r="K70" s="183"/>
-      <c r="L70" s="183"/>
-      <c r="M70" s="183"/>
-      <c r="N70" s="184"/>
-      <c r="O70" s="175" t="s">
+      <c r="D70" s="159"/>
+      <c r="E70" s="159"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="159"/>
+      <c r="H70" s="159"/>
+      <c r="I70" s="159"/>
+      <c r="J70" s="159"/>
+      <c r="K70" s="159"/>
+      <c r="L70" s="159"/>
+      <c r="M70" s="159"/>
+      <c r="N70" s="160"/>
+      <c r="O70" s="151" t="s">
         <v>133</v>
       </c>
-      <c r="P70" s="176"/>
-      <c r="Q70" s="176"/>
-      <c r="R70" s="176"/>
-      <c r="S70" s="177"/>
-      <c r="T70" s="178" t="s">
+      <c r="P70" s="152"/>
+      <c r="Q70" s="152"/>
+      <c r="R70" s="152"/>
+      <c r="S70" s="153"/>
+      <c r="T70" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="U70" s="173"/>
-      <c r="V70" s="173"/>
-      <c r="W70" s="174"/>
-      <c r="X70" s="178">
+      <c r="U70" s="149"/>
+      <c r="V70" s="149"/>
+      <c r="W70" s="150"/>
+      <c r="X70" s="154">
         <v>6</v>
       </c>
-      <c r="Y70" s="173"/>
-      <c r="Z70" s="174"/>
+      <c r="Y70" s="149"/>
+      <c r="Z70" s="150"/>
     </row>
     <row r="71" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A71" s="70" t="s">
@@ -7161,38 +7165,38 @@
       <c r="B71" s="70" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="172" t="s">
+      <c r="C71" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="D71" s="183"/>
-      <c r="E71" s="183"/>
-      <c r="F71" s="183"/>
-      <c r="G71" s="183"/>
-      <c r="H71" s="183"/>
-      <c r="I71" s="183"/>
-      <c r="J71" s="183"/>
-      <c r="K71" s="183"/>
-      <c r="L71" s="183"/>
-      <c r="M71" s="183"/>
-      <c r="N71" s="184"/>
-      <c r="O71" s="175" t="s">
+      <c r="D71" s="159"/>
+      <c r="E71" s="159"/>
+      <c r="F71" s="159"/>
+      <c r="G71" s="159"/>
+      <c r="H71" s="159"/>
+      <c r="I71" s="159"/>
+      <c r="J71" s="159"/>
+      <c r="K71" s="159"/>
+      <c r="L71" s="159"/>
+      <c r="M71" s="159"/>
+      <c r="N71" s="160"/>
+      <c r="O71" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="P71" s="176"/>
-      <c r="Q71" s="176"/>
-      <c r="R71" s="176"/>
-      <c r="S71" s="177"/>
-      <c r="T71" s="178" t="s">
+      <c r="P71" s="152"/>
+      <c r="Q71" s="152"/>
+      <c r="R71" s="152"/>
+      <c r="S71" s="153"/>
+      <c r="T71" s="154" t="s">
         <v>138</v>
       </c>
-      <c r="U71" s="173"/>
-      <c r="V71" s="173"/>
-      <c r="W71" s="174"/>
-      <c r="X71" s="178">
+      <c r="U71" s="149"/>
+      <c r="V71" s="149"/>
+      <c r="W71" s="150"/>
+      <c r="X71" s="154">
         <v>6</v>
       </c>
-      <c r="Y71" s="173"/>
-      <c r="Z71" s="174"/>
+      <c r="Y71" s="149"/>
+      <c r="Z71" s="150"/>
     </row>
     <row r="72" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A72" s="70" t="s">
@@ -7201,38 +7205,38 @@
       <c r="B72" s="70" t="s">
         <v>211</v>
       </c>
-      <c r="C72" s="172" t="s">
+      <c r="C72" s="148" t="s">
         <v>212</v>
       </c>
-      <c r="D72" s="183"/>
-      <c r="E72" s="183"/>
-      <c r="F72" s="183"/>
-      <c r="G72" s="183"/>
-      <c r="H72" s="183"/>
-      <c r="I72" s="183"/>
-      <c r="J72" s="183"/>
-      <c r="K72" s="183"/>
-      <c r="L72" s="183"/>
-      <c r="M72" s="183"/>
-      <c r="N72" s="184"/>
-      <c r="O72" s="175" t="s">
+      <c r="D72" s="159"/>
+      <c r="E72" s="159"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="159"/>
+      <c r="H72" s="159"/>
+      <c r="I72" s="159"/>
+      <c r="J72" s="159"/>
+      <c r="K72" s="159"/>
+      <c r="L72" s="159"/>
+      <c r="M72" s="159"/>
+      <c r="N72" s="160"/>
+      <c r="O72" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="P72" s="176"/>
-      <c r="Q72" s="176"/>
-      <c r="R72" s="176"/>
-      <c r="S72" s="177"/>
-      <c r="T72" s="178" t="s">
+      <c r="P72" s="152"/>
+      <c r="Q72" s="152"/>
+      <c r="R72" s="152"/>
+      <c r="S72" s="153"/>
+      <c r="T72" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="U72" s="173"/>
-      <c r="V72" s="173"/>
-      <c r="W72" s="174"/>
-      <c r="X72" s="178">
+      <c r="U72" s="149"/>
+      <c r="V72" s="149"/>
+      <c r="W72" s="150"/>
+      <c r="X72" s="154">
         <v>6</v>
       </c>
-      <c r="Y72" s="173"/>
-      <c r="Z72" s="174"/>
+      <c r="Y72" s="149"/>
+      <c r="Z72" s="150"/>
     </row>
     <row r="73" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A73" s="70">
@@ -7241,38 +7245,38 @@
       <c r="B73" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C73" s="172" t="s">
+      <c r="C73" s="148" t="s">
         <v>214</v>
       </c>
-      <c r="D73" s="173"/>
-      <c r="E73" s="173"/>
-      <c r="F73" s="173"/>
-      <c r="G73" s="173"/>
-      <c r="H73" s="173"/>
-      <c r="I73" s="173"/>
-      <c r="J73" s="173"/>
-      <c r="K73" s="173"/>
-      <c r="L73" s="173"/>
-      <c r="M73" s="173"/>
-      <c r="N73" s="174"/>
-      <c r="O73" s="175" t="s">
+      <c r="D73" s="149"/>
+      <c r="E73" s="149"/>
+      <c r="F73" s="149"/>
+      <c r="G73" s="149"/>
+      <c r="H73" s="149"/>
+      <c r="I73" s="149"/>
+      <c r="J73" s="149"/>
+      <c r="K73" s="149"/>
+      <c r="L73" s="149"/>
+      <c r="M73" s="149"/>
+      <c r="N73" s="150"/>
+      <c r="O73" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P73" s="176"/>
-      <c r="Q73" s="176"/>
-      <c r="R73" s="176"/>
-      <c r="S73" s="177"/>
-      <c r="T73" s="178" t="s">
+      <c r="P73" s="152"/>
+      <c r="Q73" s="152"/>
+      <c r="R73" s="152"/>
+      <c r="S73" s="153"/>
+      <c r="T73" s="154" t="s">
         <v>154</v>
       </c>
-      <c r="U73" s="173"/>
-      <c r="V73" s="173"/>
-      <c r="W73" s="174"/>
-      <c r="X73" s="180">
+      <c r="U73" s="149"/>
+      <c r="V73" s="149"/>
+      <c r="W73" s="150"/>
+      <c r="X73" s="156">
         <v>1</v>
       </c>
-      <c r="Y73" s="181"/>
-      <c r="Z73" s="182"/>
+      <c r="Y73" s="157"/>
+      <c r="Z73" s="158"/>
     </row>
     <row r="74" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A74" s="70" t="s">
@@ -7281,38 +7285,38 @@
       <c r="B74" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C74" s="172" t="s">
+      <c r="C74" s="148" t="s">
         <v>216</v>
       </c>
-      <c r="D74" s="173"/>
-      <c r="E74" s="173"/>
-      <c r="F74" s="173"/>
-      <c r="G74" s="173"/>
-      <c r="H74" s="173"/>
-      <c r="I74" s="173"/>
-      <c r="J74" s="173"/>
-      <c r="K74" s="173"/>
-      <c r="L74" s="173"/>
-      <c r="M74" s="173"/>
-      <c r="N74" s="174"/>
-      <c r="O74" s="175" t="s">
+      <c r="D74" s="149"/>
+      <c r="E74" s="149"/>
+      <c r="F74" s="149"/>
+      <c r="G74" s="149"/>
+      <c r="H74" s="149"/>
+      <c r="I74" s="149"/>
+      <c r="J74" s="149"/>
+      <c r="K74" s="149"/>
+      <c r="L74" s="149"/>
+      <c r="M74" s="149"/>
+      <c r="N74" s="150"/>
+      <c r="O74" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P74" s="176"/>
-      <c r="Q74" s="176"/>
-      <c r="R74" s="176"/>
-      <c r="S74" s="177"/>
-      <c r="T74" s="178" t="s">
+      <c r="P74" s="152"/>
+      <c r="Q74" s="152"/>
+      <c r="R74" s="152"/>
+      <c r="S74" s="153"/>
+      <c r="T74" s="154" t="s">
         <v>157</v>
       </c>
-      <c r="U74" s="173"/>
-      <c r="V74" s="173"/>
-      <c r="W74" s="174"/>
-      <c r="X74" s="180">
+      <c r="U74" s="149"/>
+      <c r="V74" s="149"/>
+      <c r="W74" s="150"/>
+      <c r="X74" s="156">
         <v>4</v>
       </c>
-      <c r="Y74" s="181"/>
-      <c r="Z74" s="182"/>
+      <c r="Y74" s="157"/>
+      <c r="Z74" s="158"/>
     </row>
     <row r="75" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A75" s="70" t="s">
@@ -7321,38 +7325,38 @@
       <c r="B75" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C75" s="172" t="s">
+      <c r="C75" s="148" t="s">
         <v>218</v>
       </c>
-      <c r="D75" s="173"/>
-      <c r="E75" s="173"/>
-      <c r="F75" s="173"/>
-      <c r="G75" s="173"/>
-      <c r="H75" s="173"/>
-      <c r="I75" s="173"/>
-      <c r="J75" s="173"/>
-      <c r="K75" s="173"/>
-      <c r="L75" s="173"/>
-      <c r="M75" s="173"/>
-      <c r="N75" s="174"/>
-      <c r="O75" s="175" t="s">
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="149"/>
+      <c r="H75" s="149"/>
+      <c r="I75" s="149"/>
+      <c r="J75" s="149"/>
+      <c r="K75" s="149"/>
+      <c r="L75" s="149"/>
+      <c r="M75" s="149"/>
+      <c r="N75" s="150"/>
+      <c r="O75" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="P75" s="176"/>
-      <c r="Q75" s="176"/>
-      <c r="R75" s="176"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="178" t="s">
+      <c r="P75" s="152"/>
+      <c r="Q75" s="152"/>
+      <c r="R75" s="152"/>
+      <c r="S75" s="153"/>
+      <c r="T75" s="154" t="s">
         <v>160</v>
       </c>
-      <c r="U75" s="173"/>
-      <c r="V75" s="173"/>
-      <c r="W75" s="174"/>
-      <c r="X75" s="180">
+      <c r="U75" s="149"/>
+      <c r="V75" s="149"/>
+      <c r="W75" s="150"/>
+      <c r="X75" s="156">
         <v>1</v>
       </c>
-      <c r="Y75" s="181"/>
-      <c r="Z75" s="182"/>
+      <c r="Y75" s="157"/>
+      <c r="Z75" s="158"/>
     </row>
     <row r="76" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A76" s="70" t="s">
@@ -7361,38 +7365,38 @@
       <c r="B76" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C76" s="172" t="s">
+      <c r="C76" s="148" t="s">
         <v>220</v>
       </c>
-      <c r="D76" s="173"/>
-      <c r="E76" s="173"/>
-      <c r="F76" s="173"/>
-      <c r="G76" s="173"/>
-      <c r="H76" s="173"/>
-      <c r="I76" s="173"/>
-      <c r="J76" s="173"/>
-      <c r="K76" s="173"/>
-      <c r="L76" s="173"/>
-      <c r="M76" s="173"/>
-      <c r="N76" s="174"/>
-      <c r="O76" s="175" t="s">
+      <c r="D76" s="149"/>
+      <c r="E76" s="149"/>
+      <c r="F76" s="149"/>
+      <c r="G76" s="149"/>
+      <c r="H76" s="149"/>
+      <c r="I76" s="149"/>
+      <c r="J76" s="149"/>
+      <c r="K76" s="149"/>
+      <c r="L76" s="149"/>
+      <c r="M76" s="149"/>
+      <c r="N76" s="150"/>
+      <c r="O76" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="P76" s="176"/>
-      <c r="Q76" s="176"/>
-      <c r="R76" s="176"/>
-      <c r="S76" s="177"/>
-      <c r="T76" s="178" t="s">
+      <c r="P76" s="152"/>
+      <c r="Q76" s="152"/>
+      <c r="R76" s="152"/>
+      <c r="S76" s="153"/>
+      <c r="T76" s="154" t="s">
         <v>163</v>
       </c>
-      <c r="U76" s="173"/>
-      <c r="V76" s="173"/>
-      <c r="W76" s="174"/>
-      <c r="X76" s="180">
+      <c r="U76" s="149"/>
+      <c r="V76" s="149"/>
+      <c r="W76" s="150"/>
+      <c r="X76" s="156">
         <v>1</v>
       </c>
-      <c r="Y76" s="181"/>
-      <c r="Z76" s="182"/>
+      <c r="Y76" s="157"/>
+      <c r="Z76" s="158"/>
     </row>
     <row r="77" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A77" s="70">
@@ -7401,38 +7405,38 @@
       <c r="B77" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="C77" s="172" t="s">
+      <c r="C77" s="148" t="s">
         <v>222</v>
       </c>
-      <c r="D77" s="173"/>
-      <c r="E77" s="173"/>
-      <c r="F77" s="173"/>
-      <c r="G77" s="173"/>
-      <c r="H77" s="173"/>
-      <c r="I77" s="173"/>
-      <c r="J77" s="173"/>
-      <c r="K77" s="173"/>
-      <c r="L77" s="173"/>
-      <c r="M77" s="173"/>
-      <c r="N77" s="174"/>
-      <c r="O77" s="178" t="s">
+      <c r="D77" s="149"/>
+      <c r="E77" s="149"/>
+      <c r="F77" s="149"/>
+      <c r="G77" s="149"/>
+      <c r="H77" s="149"/>
+      <c r="I77" s="149"/>
+      <c r="J77" s="149"/>
+      <c r="K77" s="149"/>
+      <c r="L77" s="149"/>
+      <c r="M77" s="149"/>
+      <c r="N77" s="150"/>
+      <c r="O77" s="154" t="s">
         <v>167</v>
       </c>
-      <c r="P77" s="173"/>
-      <c r="Q77" s="173"/>
-      <c r="R77" s="173"/>
-      <c r="S77" s="174"/>
-      <c r="T77" s="178" t="s">
+      <c r="P77" s="149"/>
+      <c r="Q77" s="149"/>
+      <c r="R77" s="149"/>
+      <c r="S77" s="150"/>
+      <c r="T77" s="154" t="s">
         <v>168</v>
       </c>
-      <c r="U77" s="173"/>
-      <c r="V77" s="173"/>
-      <c r="W77" s="174"/>
-      <c r="X77" s="178">
+      <c r="U77" s="149"/>
+      <c r="V77" s="149"/>
+      <c r="W77" s="150"/>
+      <c r="X77" s="154">
         <v>1</v>
       </c>
-      <c r="Y77" s="173"/>
-      <c r="Z77" s="174"/>
+      <c r="Y77" s="149"/>
+      <c r="Z77" s="150"/>
     </row>
     <row r="78" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A78" s="70" t="s">
@@ -7441,38 +7445,38 @@
       <c r="B78" s="70" t="s">
         <v>223</v>
       </c>
-      <c r="C78" s="172" t="s">
+      <c r="C78" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="173"/>
-      <c r="E78" s="173"/>
-      <c r="F78" s="173"/>
-      <c r="G78" s="173"/>
-      <c r="H78" s="173"/>
-      <c r="I78" s="173"/>
-      <c r="J78" s="173"/>
-      <c r="K78" s="173"/>
-      <c r="L78" s="173"/>
-      <c r="M78" s="173"/>
-      <c r="N78" s="174"/>
-      <c r="O78" s="175" t="s">
+      <c r="D78" s="149"/>
+      <c r="E78" s="149"/>
+      <c r="F78" s="149"/>
+      <c r="G78" s="149"/>
+      <c r="H78" s="149"/>
+      <c r="I78" s="149"/>
+      <c r="J78" s="149"/>
+      <c r="K78" s="149"/>
+      <c r="L78" s="149"/>
+      <c r="M78" s="149"/>
+      <c r="N78" s="150"/>
+      <c r="O78" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P78" s="176"/>
-      <c r="Q78" s="176"/>
-      <c r="R78" s="176"/>
-      <c r="S78" s="177"/>
-      <c r="T78" s="178" t="s">
+      <c r="P78" s="152"/>
+      <c r="Q78" s="152"/>
+      <c r="R78" s="152"/>
+      <c r="S78" s="153"/>
+      <c r="T78" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="U78" s="173"/>
-      <c r="V78" s="173"/>
-      <c r="W78" s="174"/>
-      <c r="X78" s="178">
+      <c r="U78" s="149"/>
+      <c r="V78" s="149"/>
+      <c r="W78" s="150"/>
+      <c r="X78" s="154">
         <v>2</v>
       </c>
-      <c r="Y78" s="173"/>
-      <c r="Z78" s="174"/>
+      <c r="Y78" s="149"/>
+      <c r="Z78" s="150"/>
     </row>
     <row r="79" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A79" s="70" t="s">
@@ -7481,38 +7485,38 @@
       <c r="B79" s="70" t="s">
         <v>224</v>
       </c>
-      <c r="C79" s="172" t="s">
+      <c r="C79" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="D79" s="173"/>
-      <c r="E79" s="173"/>
-      <c r="F79" s="173"/>
-      <c r="G79" s="173"/>
-      <c r="H79" s="173"/>
-      <c r="I79" s="173"/>
-      <c r="J79" s="173"/>
-      <c r="K79" s="173"/>
-      <c r="L79" s="173"/>
-      <c r="M79" s="173"/>
-      <c r="N79" s="174"/>
-      <c r="O79" s="175" t="s">
+      <c r="D79" s="149"/>
+      <c r="E79" s="149"/>
+      <c r="F79" s="149"/>
+      <c r="G79" s="149"/>
+      <c r="H79" s="149"/>
+      <c r="I79" s="149"/>
+      <c r="J79" s="149"/>
+      <c r="K79" s="149"/>
+      <c r="L79" s="149"/>
+      <c r="M79" s="149"/>
+      <c r="N79" s="150"/>
+      <c r="O79" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P79" s="176"/>
-      <c r="Q79" s="176"/>
-      <c r="R79" s="176"/>
-      <c r="S79" s="177"/>
-      <c r="T79" s="178" t="s">
+      <c r="P79" s="152"/>
+      <c r="Q79" s="152"/>
+      <c r="R79" s="152"/>
+      <c r="S79" s="153"/>
+      <c r="T79" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="U79" s="173"/>
-      <c r="V79" s="173"/>
-      <c r="W79" s="174"/>
-      <c r="X79" s="178">
+      <c r="U79" s="149"/>
+      <c r="V79" s="149"/>
+      <c r="W79" s="150"/>
+      <c r="X79" s="154">
         <v>2</v>
       </c>
-      <c r="Y79" s="173"/>
-      <c r="Z79" s="174"/>
+      <c r="Y79" s="149"/>
+      <c r="Z79" s="150"/>
     </row>
     <row r="80" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A80" s="70" t="s">
@@ -7521,38 +7525,38 @@
       <c r="B80" s="70" t="s">
         <v>226</v>
       </c>
-      <c r="C80" s="172" t="s">
+      <c r="C80" s="148" t="s">
         <v>227</v>
       </c>
-      <c r="D80" s="173"/>
-      <c r="E80" s="173"/>
-      <c r="F80" s="173"/>
-      <c r="G80" s="173"/>
-      <c r="H80" s="173"/>
-      <c r="I80" s="173"/>
-      <c r="J80" s="173"/>
-      <c r="K80" s="173"/>
-      <c r="L80" s="173"/>
-      <c r="M80" s="173"/>
-      <c r="N80" s="174"/>
-      <c r="O80" s="175" t="s">
+      <c r="D80" s="149"/>
+      <c r="E80" s="149"/>
+      <c r="F80" s="149"/>
+      <c r="G80" s="149"/>
+      <c r="H80" s="149"/>
+      <c r="I80" s="149"/>
+      <c r="J80" s="149"/>
+      <c r="K80" s="149"/>
+      <c r="L80" s="149"/>
+      <c r="M80" s="149"/>
+      <c r="N80" s="150"/>
+      <c r="O80" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P80" s="176"/>
-      <c r="Q80" s="176"/>
-      <c r="R80" s="176"/>
-      <c r="S80" s="177"/>
-      <c r="T80" s="178" t="s">
+      <c r="P80" s="152"/>
+      <c r="Q80" s="152"/>
+      <c r="R80" s="152"/>
+      <c r="S80" s="153"/>
+      <c r="T80" s="154" t="s">
         <v>176</v>
       </c>
-      <c r="U80" s="173"/>
-      <c r="V80" s="173"/>
-      <c r="W80" s="174"/>
-      <c r="X80" s="178">
+      <c r="U80" s="149"/>
+      <c r="V80" s="149"/>
+      <c r="W80" s="150"/>
+      <c r="X80" s="154">
         <v>2</v>
       </c>
-      <c r="Y80" s="173"/>
-      <c r="Z80" s="174"/>
+      <c r="Y80" s="149"/>
+      <c r="Z80" s="150"/>
     </row>
     <row r="81" spans="1:26" s="7" customFormat="1" ht="16.5" customHeight="1">
       <c r="A81" s="70" t="s">
@@ -7561,69 +7565,69 @@
       <c r="B81" s="70" t="s">
         <v>228</v>
       </c>
-      <c r="C81" s="172" t="s">
+      <c r="C81" s="148" t="s">
         <v>229</v>
       </c>
-      <c r="D81" s="173"/>
-      <c r="E81" s="173"/>
-      <c r="F81" s="173"/>
-      <c r="G81" s="173"/>
-      <c r="H81" s="173"/>
-      <c r="I81" s="173"/>
-      <c r="J81" s="173"/>
-      <c r="K81" s="173"/>
-      <c r="L81" s="173"/>
-      <c r="M81" s="173"/>
-      <c r="N81" s="174"/>
-      <c r="O81" s="175" t="s">
+      <c r="D81" s="149"/>
+      <c r="E81" s="149"/>
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
+      <c r="H81" s="149"/>
+      <c r="I81" s="149"/>
+      <c r="J81" s="149"/>
+      <c r="K81" s="149"/>
+      <c r="L81" s="149"/>
+      <c r="M81" s="149"/>
+      <c r="N81" s="150"/>
+      <c r="O81" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="P81" s="176"/>
-      <c r="Q81" s="176"/>
-      <c r="R81" s="176"/>
-      <c r="S81" s="177"/>
-      <c r="T81" s="178" t="s">
+      <c r="P81" s="152"/>
+      <c r="Q81" s="152"/>
+      <c r="R81" s="152"/>
+      <c r="S81" s="153"/>
+      <c r="T81" s="154" t="s">
         <v>179</v>
       </c>
-      <c r="U81" s="173"/>
-      <c r="V81" s="173"/>
-      <c r="W81" s="174"/>
-      <c r="X81" s="178">
+      <c r="U81" s="149"/>
+      <c r="V81" s="149"/>
+      <c r="W81" s="150"/>
+      <c r="X81" s="154">
         <v>2</v>
       </c>
-      <c r="Y81" s="173"/>
-      <c r="Z81" s="174"/>
-    </row>
-    <row r="82" spans="1:26" s="7" customFormat="1" ht="20.350000000000001" customHeight="1">
+      <c r="Y81" s="149"/>
+      <c r="Z81" s="150"/>
+    </row>
+    <row r="82" spans="1:26" s="7" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="A82" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C82" s="179"/>
-      <c r="D82" s="179"/>
-      <c r="E82" s="179"/>
-      <c r="F82" s="179"/>
-      <c r="G82" s="179"/>
-      <c r="H82" s="179"/>
-      <c r="I82" s="179"/>
-      <c r="J82" s="179"/>
-      <c r="K82" s="179"/>
-      <c r="L82" s="179"/>
-      <c r="M82" s="179"/>
-      <c r="N82" s="179"/>
-      <c r="O82" s="179"/>
-      <c r="P82" s="179"/>
-      <c r="Q82" s="179"/>
-      <c r="R82" s="179"/>
-      <c r="S82" s="179"/>
-      <c r="T82" s="179"/>
-      <c r="U82" s="179"/>
-      <c r="V82" s="179"/>
-      <c r="W82" s="179"/>
-      <c r="X82" s="179"/>
-      <c r="Y82" s="179"/>
-      <c r="Z82" s="179"/>
-    </row>
-    <row r="83" spans="1:26" ht="15.75">
+      <c r="C82" s="155"/>
+      <c r="D82" s="155"/>
+      <c r="E82" s="155"/>
+      <c r="F82" s="155"/>
+      <c r="G82" s="155"/>
+      <c r="H82" s="155"/>
+      <c r="I82" s="155"/>
+      <c r="J82" s="155"/>
+      <c r="K82" s="155"/>
+      <c r="L82" s="155"/>
+      <c r="M82" s="155"/>
+      <c r="N82" s="155"/>
+      <c r="O82" s="155"/>
+      <c r="P82" s="155"/>
+      <c r="Q82" s="155"/>
+      <c r="R82" s="155"/>
+      <c r="S82" s="155"/>
+      <c r="T82" s="155"/>
+      <c r="U82" s="155"/>
+      <c r="V82" s="155"/>
+      <c r="W82" s="155"/>
+      <c r="X82" s="155"/>
+      <c r="Y82" s="155"/>
+      <c r="Z82" s="155"/>
+    </row>
+    <row r="83" spans="1:26" ht="15.6">
       <c r="A83" s="73"/>
       <c r="B83" s="74"/>
       <c r="C83" s="74"/>
@@ -7936,204 +7940,204 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.796875" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="56.33203125" customWidth="1"/>
-    <col min="3" max="18" width="3.9296875" customWidth="1"/>
-    <col min="19" max="20" width="4.3984375" customWidth="1"/>
-    <col min="21" max="26" width="4.9296875" customWidth="1"/>
+    <col min="3" max="18" width="3.88671875" customWidth="1"/>
+    <col min="19" max="20" width="4.44140625" customWidth="1"/>
+    <col min="21" max="26" width="4.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
       <c r="W1" s="60"/>
       <c r="X1" s="60"/>
       <c r="Y1" s="60"/>
       <c r="Z1" s="60"/>
     </row>
     <row r="2" spans="1:26" ht="15">
-      <c r="A2" s="119"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
+      <c r="A2" s="212"/>
+      <c r="B2" s="212"/>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="212"/>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
       <c r="W2" s="60"/>
       <c r="X2" s="60"/>
       <c r="Y2" s="60"/>
       <c r="Z2" s="60"/>
     </row>
     <row r="3" spans="1:26" ht="15">
-      <c r="A3" s="119"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="119"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
+      <c r="A3" s="212"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="212"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212"/>
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
       <c r="W3" s="60"/>
       <c r="X3" s="60"/>
       <c r="Y3" s="60"/>
       <c r="Z3" s="60"/>
     </row>
     <row r="4" spans="1:26" ht="15">
-      <c r="A4" s="119"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="119"/>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="119"/>
-      <c r="V4" s="119"/>
+      <c r="A4" s="212"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="212"/>
+      <c r="H4" s="212"/>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="212"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="212"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="212"/>
+      <c r="T4" s="212"/>
+      <c r="U4" s="212"/>
+      <c r="V4" s="212"/>
       <c r="W4" s="60"/>
       <c r="X4" s="60"/>
       <c r="Y4" s="60"/>
       <c r="Z4" s="60"/>
     </row>
     <row r="5" spans="1:26" ht="15">
-      <c r="A5" s="119"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
-      <c r="N5" s="119"/>
-      <c r="O5" s="119"/>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="119"/>
+      <c r="A5" s="212"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="212"/>
+      <c r="G5" s="212"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="212"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="212"/>
+      <c r="L5" s="212"/>
+      <c r="M5" s="212"/>
+      <c r="N5" s="212"/>
+      <c r="O5" s="212"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="212"/>
+      <c r="R5" s="212"/>
+      <c r="S5" s="212"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
+      <c r="V5" s="212"/>
       <c r="W5" s="60"/>
       <c r="X5" s="60"/>
       <c r="Y5" s="60"/>
       <c r="Z5" s="60"/>
     </row>
-    <row r="6" spans="1:26" ht="29.65">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="120"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="120"/>
-      <c r="P6" s="120"/>
-      <c r="Q6" s="120"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="120"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-    </row>
-    <row r="7" spans="1:26" s="63" customFormat="1" ht="17.25">
-      <c r="A7" s="123" t="s">
+      <c r="B6" s="213"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
+      <c r="H6" s="213"/>
+      <c r="I6" s="213"/>
+      <c r="J6" s="213"/>
+      <c r="K6" s="213"/>
+      <c r="L6" s="213"/>
+      <c r="M6" s="213"/>
+      <c r="N6" s="213"/>
+      <c r="O6" s="213"/>
+      <c r="P6" s="213"/>
+      <c r="Q6" s="213"/>
+      <c r="R6" s="213"/>
+      <c r="S6" s="213"/>
+      <c r="T6" s="213"/>
+      <c r="U6" s="213"/>
+      <c r="V6" s="213"/>
+      <c r="W6" s="213"/>
+      <c r="X6" s="213"/>
+      <c r="Y6" s="213"/>
+      <c r="Z6" s="213"/>
+    </row>
+    <row r="7" spans="1:26" s="63" customFormat="1" ht="17.399999999999999">
+      <c r="A7" s="214" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="123"/>
+      <c r="B7" s="214"/>
       <c r="C7" s="82" t="s">
         <v>80</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="111" t="str">
+      <c r="G7" s="205" t="str">
         <f>'ใบงาน Agilent_JOB 7.1'!F7</f>
         <v>xxx</v>
       </c>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -8141,7 +8145,7 @@
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
-      <c r="S7" s="216" t="s">
+      <c r="S7" s="96" t="s">
         <v>67</v>
       </c>
       <c r="W7" s="86" t="str">
@@ -8166,13 +8170,13 @@
       <c r="D8" s="62"/>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
-      <c r="G8" s="122" t="str">
+      <c r="G8" s="215" t="str">
         <f>'ใบงาน Agilent_JOB 7.1'!F9</f>
         <v>K9801-60087</v>
       </c>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
+      <c r="H8" s="215"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="215"/>
       <c r="K8" s="56"/>
       <c r="L8" s="56"/>
       <c r="M8" s="56"/>
@@ -8190,22 +8194,22 @@
         <v>PO12345</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="7" customFormat="1" ht="19.149999999999999" customHeight="1">
-      <c r="A9" s="123" t="s">
+    <row r="9" spans="1:26" s="7" customFormat="1" ht="19.2" customHeight="1">
+      <c r="A9" s="214" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="123"/>
+      <c r="B9" s="214"/>
       <c r="C9" s="63"/>
       <c r="D9" s="63"/>
       <c r="E9" s="63"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="122" t="str">
+      <c r="G9" s="215" t="str">
         <f>'ใบงาน Agilent_JOB 7.2'!F9</f>
         <v>K9801-60116</v>
       </c>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="215"/>
+      <c r="J9" s="215"/>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
       <c r="N9" s="14"/>
@@ -8214,7 +8218,7 @@
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
     </row>
-    <row r="10" spans="1:26" s="7" customFormat="1" ht="13.5">
+    <row r="10" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A10" s="56" t="s">
         <v>84</v>
       </c>
@@ -8223,17 +8227,17 @@
         <v>40</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="111" t="s">
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="205"/>
+      <c r="J10" s="205"/>
       <c r="K10" s="57"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
@@ -8243,18 +8247,18 @@
       <c r="Q10" s="14"/>
       <c r="R10" s="14"/>
     </row>
-    <row r="11" spans="1:26" s="7" customFormat="1" ht="13.5">
-      <c r="B11" s="109"/>
+    <row r="11" spans="1:26" s="7" customFormat="1" ht="13.8">
+      <c r="B11" s="100"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
-      <c r="G11" s="111" t="s">
+      <c r="G11" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="205"/>
+      <c r="J11" s="205"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
@@ -8263,28 +8267,28 @@
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
-      <c r="S11" s="124" t="s">
+      <c r="S11" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="T11" s="124"/>
-      <c r="U11" s="124"/>
-      <c r="V11" s="124"/>
-    </row>
-    <row r="12" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="T11" s="99"/>
+      <c r="U11" s="99"/>
+      <c r="V11" s="99"/>
+    </row>
+    <row r="12" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A12" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="109"/>
+      <c r="B12" s="100"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="111" t="s">
+      <c r="G12" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="205"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
@@ -8293,14 +8297,14 @@
       <c r="P12" s="14"/>
       <c r="Q12" s="14"/>
       <c r="R12" s="14"/>
-      <c r="S12" s="124"/>
-      <c r="T12" s="124"/>
-      <c r="U12" s="124"/>
-      <c r="V12" s="124"/>
-    </row>
-    <row r="13" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="S12" s="99"/>
+      <c r="T12" s="99"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="99"/>
+    </row>
+    <row r="13" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A13" s="14"/>
-      <c r="B13" s="110"/>
+      <c r="B13" s="217"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
@@ -8320,348 +8324,348 @@
       <c r="S13" s="14"/>
       <c r="T13" s="14"/>
     </row>
-    <row r="14" spans="1:26" s="7" customFormat="1" ht="13.5">
-      <c r="A14" s="112" t="s">
+    <row r="14" spans="1:26" s="7" customFormat="1" ht="13.8">
+      <c r="A14" s="206" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="99" t="s">
+      <c r="C14" s="198" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="99" t="s">
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="207"/>
+      <c r="G14" s="207"/>
+      <c r="H14" s="208"/>
+      <c r="I14" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="114"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="99" t="s">
+      <c r="J14" s="207"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="208"/>
+      <c r="O14" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="100"/>
-      <c r="T14" s="101"/>
-      <c r="U14" s="105" t="s">
+      <c r="P14" s="199"/>
+      <c r="Q14" s="199"/>
+      <c r="R14" s="199"/>
+      <c r="S14" s="199"/>
+      <c r="T14" s="200"/>
+      <c r="U14" s="204" t="s">
         <v>88</v>
       </c>
-      <c r="V14" s="105"/>
-      <c r="W14" s="105"/>
-      <c r="X14" s="105"/>
-      <c r="Y14" s="105"/>
-      <c r="Z14" s="105"/>
-    </row>
-    <row r="15" spans="1:26" s="7" customFormat="1" ht="13.5">
-      <c r="A15" s="113"/>
-      <c r="B15" s="112"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="117"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="104"/>
-      <c r="U15" s="105"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="105"/>
-      <c r="X15" s="105"/>
-      <c r="Y15" s="105"/>
-      <c r="Z15" s="105"/>
-    </row>
-    <row r="16" spans="1:26" s="65" customFormat="1" ht="17.25">
-      <c r="A16" s="106">
+      <c r="V14" s="204"/>
+      <c r="W14" s="204"/>
+      <c r="X14" s="204"/>
+      <c r="Y14" s="204"/>
+      <c r="Z14" s="204"/>
+    </row>
+    <row r="15" spans="1:26" s="7" customFormat="1" ht="13.8">
+      <c r="A15" s="118"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
+      <c r="F15" s="210"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="209"/>
+      <c r="J15" s="210"/>
+      <c r="K15" s="210"/>
+      <c r="L15" s="210"/>
+      <c r="M15" s="210"/>
+      <c r="N15" s="211"/>
+      <c r="O15" s="201"/>
+      <c r="P15" s="202"/>
+      <c r="Q15" s="202"/>
+      <c r="R15" s="202"/>
+      <c r="S15" s="202"/>
+      <c r="T15" s="203"/>
+      <c r="U15" s="204"/>
+      <c r="V15" s="204"/>
+      <c r="W15" s="204"/>
+      <c r="X15" s="204"/>
+      <c r="Y15" s="204"/>
+      <c r="Z15" s="204"/>
+    </row>
+    <row r="16" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
+      <c r="A16" s="195">
         <v>1</v>
       </c>
       <c r="B16" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
-    </row>
-    <row r="17" spans="1:26" s="65" customFormat="1" ht="17.25">
-      <c r="A17" s="107"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="193"/>
+      <c r="G16" s="193"/>
+      <c r="H16" s="193"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="193"/>
+      <c r="L16" s="193"/>
+      <c r="M16" s="193"/>
+      <c r="N16" s="193"/>
+      <c r="O16" s="193"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="193"/>
+      <c r="R16" s="193"/>
+      <c r="S16" s="193"/>
+      <c r="T16" s="193"/>
+      <c r="U16" s="193"/>
+      <c r="V16" s="193"/>
+      <c r="W16" s="193"/>
+      <c r="X16" s="193"/>
+      <c r="Y16" s="193"/>
+      <c r="Z16" s="193"/>
+    </row>
+    <row r="17" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
+      <c r="A17" s="196"/>
       <c r="B17" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-    </row>
-    <row r="18" spans="1:26" s="65" customFormat="1" ht="17.25">
-      <c r="A18" s="107"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="193"/>
+      <c r="G17" s="193"/>
+      <c r="H17" s="193"/>
+      <c r="I17" s="193"/>
+      <c r="J17" s="193"/>
+      <c r="K17" s="193"/>
+      <c r="L17" s="193"/>
+      <c r="M17" s="193"/>
+      <c r="N17" s="193"/>
+      <c r="O17" s="193"/>
+      <c r="P17" s="193"/>
+      <c r="Q17" s="193"/>
+      <c r="R17" s="193"/>
+      <c r="S17" s="193"/>
+      <c r="T17" s="193"/>
+      <c r="U17" s="193"/>
+      <c r="V17" s="193"/>
+      <c r="W17" s="193"/>
+      <c r="X17" s="193"/>
+      <c r="Y17" s="193"/>
+      <c r="Z17" s="193"/>
+    </row>
+    <row r="18" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
+      <c r="A18" s="196"/>
       <c r="B18" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-    </row>
-    <row r="19" spans="1:26" s="65" customFormat="1" ht="17.25">
-      <c r="A19" s="107"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="193"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="193"/>
+      <c r="J18" s="193"/>
+      <c r="K18" s="193"/>
+      <c r="L18" s="193"/>
+      <c r="M18" s="193"/>
+      <c r="N18" s="193"/>
+      <c r="O18" s="193"/>
+      <c r="P18" s="193"/>
+      <c r="Q18" s="193"/>
+      <c r="R18" s="193"/>
+      <c r="S18" s="193"/>
+      <c r="T18" s="193"/>
+      <c r="U18" s="193"/>
+      <c r="V18" s="193"/>
+      <c r="W18" s="193"/>
+      <c r="X18" s="193"/>
+      <c r="Y18" s="193"/>
+      <c r="Z18" s="193"/>
+    </row>
+    <row r="19" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
+      <c r="A19" s="196"/>
       <c r="B19" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="98"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="98"/>
-      <c r="T19" s="98"/>
-      <c r="U19" s="98"/>
-      <c r="V19" s="98"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="98"/>
-    </row>
-    <row r="20" spans="1:26" s="65" customFormat="1" ht="17.25">
-      <c r="A20" s="108"/>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="193"/>
+      <c r="J19" s="193"/>
+      <c r="K19" s="193"/>
+      <c r="L19" s="193"/>
+      <c r="M19" s="193"/>
+      <c r="N19" s="193"/>
+      <c r="O19" s="193"/>
+      <c r="P19" s="193"/>
+      <c r="Q19" s="193"/>
+      <c r="R19" s="193"/>
+      <c r="S19" s="193"/>
+      <c r="T19" s="193"/>
+      <c r="U19" s="193"/>
+      <c r="V19" s="193"/>
+      <c r="W19" s="193"/>
+      <c r="X19" s="193"/>
+      <c r="Y19" s="193"/>
+      <c r="Z19" s="193"/>
+    </row>
+    <row r="20" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
+      <c r="A20" s="197"/>
       <c r="B20" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
-      <c r="V20" s="98"/>
-      <c r="W20" s="98"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="98"/>
-      <c r="Z20" s="98"/>
-    </row>
-    <row r="21" spans="1:26" s="65" customFormat="1" ht="17.25">
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="193"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="193"/>
+      <c r="J20" s="193"/>
+      <c r="K20" s="193"/>
+      <c r="L20" s="193"/>
+      <c r="M20" s="193"/>
+      <c r="N20" s="193"/>
+      <c r="O20" s="193"/>
+      <c r="P20" s="193"/>
+      <c r="Q20" s="193"/>
+      <c r="R20" s="193"/>
+      <c r="S20" s="193"/>
+      <c r="T20" s="193"/>
+      <c r="U20" s="193"/>
+      <c r="V20" s="193"/>
+      <c r="W20" s="193"/>
+      <c r="X20" s="193"/>
+      <c r="Y20" s="193"/>
+      <c r="Z20" s="193"/>
+    </row>
+    <row r="21" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
       <c r="A21" s="66">
         <v>2</v>
       </c>
       <c r="B21" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="98"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
-    </row>
-    <row r="22" spans="1:26" s="65" customFormat="1" ht="17.25">
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="F21" s="193"/>
+      <c r="G21" s="193"/>
+      <c r="H21" s="193"/>
+      <c r="I21" s="193"/>
+      <c r="J21" s="193"/>
+      <c r="K21" s="193"/>
+      <c r="L21" s="193"/>
+      <c r="M21" s="193"/>
+      <c r="N21" s="193"/>
+      <c r="O21" s="193"/>
+      <c r="P21" s="193"/>
+      <c r="Q21" s="193"/>
+      <c r="R21" s="193"/>
+      <c r="S21" s="193"/>
+      <c r="T21" s="193"/>
+      <c r="U21" s="193"/>
+      <c r="V21" s="193"/>
+      <c r="W21" s="193"/>
+      <c r="X21" s="193"/>
+      <c r="Y21" s="193"/>
+      <c r="Z21" s="193"/>
+    </row>
+    <row r="22" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
       <c r="A22" s="66">
         <v>3</v>
       </c>
       <c r="B22" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-    </row>
-    <row r="23" spans="1:26" s="65" customFormat="1" ht="17.25">
+      <c r="C22" s="193"/>
+      <c r="D22" s="193"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="193"/>
+      <c r="G22" s="193"/>
+      <c r="H22" s="193"/>
+      <c r="I22" s="193"/>
+      <c r="J22" s="193"/>
+      <c r="K22" s="193"/>
+      <c r="L22" s="193"/>
+      <c r="M22" s="193"/>
+      <c r="N22" s="193"/>
+      <c r="O22" s="193"/>
+      <c r="P22" s="193"/>
+      <c r="Q22" s="193"/>
+      <c r="R22" s="193"/>
+      <c r="S22" s="193"/>
+      <c r="T22" s="193"/>
+      <c r="U22" s="193"/>
+      <c r="V22" s="193"/>
+      <c r="W22" s="193"/>
+      <c r="X22" s="193"/>
+      <c r="Y22" s="193"/>
+      <c r="Z22" s="193"/>
+    </row>
+    <row r="23" spans="1:26" s="65" customFormat="1" ht="17.399999999999999">
       <c r="A23" s="66">
         <v>4</v>
       </c>
       <c r="B23" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="98"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="98"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="98"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="98"/>
-      <c r="V23" s="98"/>
-      <c r="W23" s="98"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="98"/>
-      <c r="Z23" s="98"/>
-    </row>
-    <row r="24" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="C23" s="193"/>
+      <c r="D23" s="193"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="193"/>
+      <c r="I23" s="193"/>
+      <c r="J23" s="193"/>
+      <c r="K23" s="193"/>
+      <c r="L23" s="193"/>
+      <c r="M23" s="193"/>
+      <c r="N23" s="193"/>
+      <c r="O23" s="193"/>
+      <c r="P23" s="193"/>
+      <c r="Q23" s="193"/>
+      <c r="R23" s="193"/>
+      <c r="S23" s="193"/>
+      <c r="T23" s="193"/>
+      <c r="U23" s="193"/>
+      <c r="V23" s="193"/>
+      <c r="W23" s="193"/>
+      <c r="X23" s="193"/>
+      <c r="Y23" s="193"/>
+      <c r="Z23" s="193"/>
+    </row>
+    <row r="24" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A24" s="8"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="97"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="175"/>
     </row>
     <row r="25" spans="1:26" s="69" customFormat="1" ht="15">
       <c r="A25" s="68"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-    </row>
-    <row r="26" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L25" s="187"/>
+      <c r="M25" s="187"/>
+    </row>
+    <row r="26" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A26" s="8"/>
-      <c r="L26" s="97"/>
-      <c r="M26" s="97"/>
-    </row>
-    <row r="27" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L26" s="175"/>
+      <c r="M26" s="175"/>
+    </row>
+    <row r="27" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A27" s="8"/>
-      <c r="L27" s="97"/>
-      <c r="M27" s="97"/>
-    </row>
-    <row r="28" spans="1:26" s="7" customFormat="1" ht="13.5">
+      <c r="L27" s="175"/>
+      <c r="M27" s="175"/>
+    </row>
+    <row r="28" spans="1:26" s="7" customFormat="1" ht="13.8">
       <c r="A28" s="8"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
+      <c r="L28" s="175"/>
+      <c r="M28" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="57">
@@ -8670,14 +8674,14 @@
     <mergeCell ref="S11:V12"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="G10:J10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
     <mergeCell ref="A1:V5"/>
     <mergeCell ref="A6:Z6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:H15"/>
@@ -8685,11 +8689,6 @@
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="I19:N19"/>
     <mergeCell ref="O19:T19"/>
@@ -8705,6 +8704,11 @@
     <mergeCell ref="I18:N18"/>
     <mergeCell ref="O18:T18"/>
     <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
     <mergeCell ref="O23:T23"/>
     <mergeCell ref="U23:Z23"/>
     <mergeCell ref="C24:F24"/>
